--- a/dados_sharepoint/atualiza_ss.xlsx
+++ b/dados_sharepoint/atualiza_ss.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos IA\Kotrik\mcs-personal\dados_sharepoint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E7419EC-0FEA-445C-A7D8-D617BB911F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09BA9BA-AC65-418B-9B7D-F15590B13D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F2D786B2-AAF2-48D2-B705-33C238AC9C38}"/>
   </bookViews>
@@ -6407,6 +6407,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{739EA7D1-82DD-4B17-A20A-28F1D73DF53F}" name="Tabela1" displayName="Tabela1" ref="A1:T489" totalsRowShown="0">
   <autoFilter ref="A1:T489" xr:uid="{739EA7D1-82DD-4B17-A20A-28F1D73DF53F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T489">
+    <sortCondition descending="1" ref="H1:H489"/>
+  </sortState>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{F209B475-E3FF-4A30-A6A2-0CFFB13BD204}" name="Cód. Colab"/>
     <tableColumn id="2" xr3:uid="{AF64177D-8E2B-4BE2-AA56-19B7A30F1A6D}" name="Nome Completo"/>
@@ -6415,7 +6418,7 @@
     <tableColumn id="5" xr3:uid="{42E7C226-CE8F-4F9E-8CC5-B5BAF93DA634}" name="Data Ingresso (Admissão)"/>
     <tableColumn id="6" xr3:uid="{A887D1C1-053C-496C-8CB5-66019853977A}" name="Data Fim (Desligamento)"/>
     <tableColumn id="7" xr3:uid="{A512B674-11B1-48CB-AE93-A0802CBEC8C2}" name="Data Alta Segurança" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{5864DEA9-3D58-46A7-A8A7-0C823D84F0D4}" name="Data Baixa Segurança" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{5864DEA9-3D58-46A7-A8A7-0C823D84F0D4}" name="Data Baixa Segurança" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{18F5E00C-39A5-4799-A7DC-6E52F239D394}" name="Empresa Contratante"/>
     <tableColumn id="10" xr3:uid="{DA5058F2-5F31-48CE-A53F-C67D450ECCA6}" name="Cliente/Obra"/>
     <tableColumn id="11" xr3:uid="{18756DA0-5DC4-4190-9D6B-DF6E52427E52}" name="Função"/>
@@ -6425,7 +6428,7 @@
     <tableColumn id="15" xr3:uid="{A9EB9175-FC89-41A4-B88C-6CF8147F3704}" name="NIE"/>
     <tableColumn id="16" xr3:uid="{01880255-6D04-4026-BFBF-9B83799FB0BC}" name="Passaporte"/>
     <tableColumn id="17" xr3:uid="{8FA76516-7C9D-4BF9-9880-D64BA44C38D7}" name="Nacionalidade"/>
-    <tableColumn id="18" xr3:uid="{8C3FF442-00AB-48BE-9868-19467FC58B57}" name="Data Nascimento" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{8C3FF442-00AB-48BE-9868-19467FC58B57}" name="Data Nascimento" dataDxfId="0"/>
     <tableColumn id="19" xr3:uid="{4F0AA66B-C222-4244-9608-6974064A8AF5}" name="Telefone"/>
     <tableColumn id="20" xr3:uid="{D8FB7768-CD0E-4F8D-AB27-402B59B0763E}" name="E-mail"/>
   </tableColumns>
@@ -6833,34 +6836,40 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>704</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>624</v>
+      </c>
+      <c r="F2">
+        <v>46113</v>
       </c>
       <c r="G2" s="1">
-        <v>46058</v>
+        <v>46063</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46113</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="L2">
-        <v>12178088103</v>
+        <v>12182388541</v>
       </c>
       <c r="M2">
-        <v>328500771</v>
+        <v>335276407</v>
       </c>
       <c r="N2" t="s">
         <v>27</v>
@@ -6869,16 +6878,16 @@
         <v>27</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>706</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
       </c>
       <c r="R2" s="1">
-        <v>32840</v>
+        <v>33559</v>
       </c>
       <c r="S2" t="s">
-        <v>29</v>
+        <v>707</v>
       </c>
       <c r="T2" t="s">
         <v>27</v>
@@ -6886,34 +6895,40 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>699</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>700</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>624</v>
+      </c>
+      <c r="F3">
+        <v>46111</v>
       </c>
       <c r="G3" s="1">
-        <v>45945</v>
+        <v>45931</v>
+      </c>
+      <c r="H3" s="1">
+        <v>46111</v>
       </c>
       <c r="I3" t="s">
         <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>701</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>12175808930</v>
+        <v>12178058358</v>
       </c>
       <c r="M3">
-        <v>325619565</v>
+        <v>328805408</v>
       </c>
       <c r="N3" t="s">
         <v>27</v>
@@ -6922,16 +6937,16 @@
         <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>702</v>
       </c>
       <c r="Q3" t="s">
         <v>27</v>
       </c>
       <c r="R3" s="1">
-        <v>31010</v>
+        <v>33345</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>703</v>
       </c>
       <c r="T3" t="s">
         <v>27</v>
@@ -6939,34 +6954,40 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>694</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>695</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>624</v>
+      </c>
+      <c r="F4">
+        <v>46106</v>
       </c>
       <c r="G4" s="1">
-        <v>46062</v>
+        <v>46055</v>
+      </c>
+      <c r="H4" s="1">
+        <v>46106</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>696</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L4">
-        <v>12182289961</v>
+        <v>12179713068</v>
       </c>
       <c r="M4">
-        <v>332901890</v>
+        <v>331127750</v>
       </c>
       <c r="N4" t="s">
         <v>27</v>
@@ -6975,16 +6996,16 @@
         <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>42</v>
+        <v>697</v>
       </c>
       <c r="Q4" t="s">
         <v>27</v>
       </c>
       <c r="R4" s="1">
-        <v>25787</v>
+        <v>32407</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>698</v>
       </c>
       <c r="T4" t="s">
         <v>27</v>
@@ -6992,34 +7013,40 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>690</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>691</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>623</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>624</v>
+      </c>
+      <c r="F5">
+        <v>46104</v>
       </c>
       <c r="G5" s="1">
-        <v>46055</v>
+        <v>46070</v>
+      </c>
+      <c r="H5" s="1">
+        <v>46104</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>418</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>283</v>
       </c>
       <c r="L5">
-        <v>12173759107</v>
+        <v>12182473225</v>
       </c>
       <c r="M5">
-        <v>323401384</v>
+        <v>334932939</v>
       </c>
       <c r="N5" t="s">
         <v>27</v>
@@ -7028,16 +7055,16 @@
         <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>48</v>
+        <v>692</v>
       </c>
       <c r="Q5" t="s">
         <v>27</v>
       </c>
       <c r="R5" s="1">
-        <v>34776</v>
+        <v>31246</v>
       </c>
       <c r="S5" t="s">
-        <v>49</v>
+        <v>693</v>
       </c>
       <c r="T5" t="s">
         <v>27</v>
@@ -7045,34 +7072,40 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>686</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>687</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F6">
+        <v>46098</v>
       </c>
       <c r="G6" s="1">
-        <v>46051</v>
+        <v>46055</v>
+      </c>
+      <c r="H6" s="1">
+        <v>46098</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="L6">
-        <v>12182662607</v>
+        <v>12178154462</v>
       </c>
       <c r="M6">
-        <v>335235387</v>
+        <v>328809365</v>
       </c>
       <c r="N6" t="s">
         <v>27</v>
@@ -7081,16 +7114,16 @@
         <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>54</v>
+        <v>688</v>
       </c>
       <c r="Q6" t="s">
         <v>27</v>
       </c>
       <c r="R6" s="1">
-        <v>28650</v>
+        <v>30597</v>
       </c>
       <c r="S6" t="s">
-        <v>55</v>
+        <v>689</v>
       </c>
       <c r="T6" t="s">
         <v>27</v>
@@ -7098,34 +7131,40 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>682</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>683</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F7">
+        <v>46096</v>
       </c>
       <c r="G7" s="1">
-        <v>45939</v>
+        <v>46028</v>
+      </c>
+      <c r="H7" s="1">
+        <v>46096</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L7">
-        <v>12178058560</v>
+        <v>12180291009</v>
       </c>
       <c r="M7">
-        <v>328282278</v>
+        <v>331104202</v>
       </c>
       <c r="N7" t="s">
         <v>27</v>
@@ -7134,16 +7173,16 @@
         <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>59</v>
+        <v>684</v>
       </c>
       <c r="Q7" t="s">
         <v>27</v>
       </c>
       <c r="R7" s="1">
-        <v>30144</v>
+        <v>27305</v>
       </c>
       <c r="S7" t="s">
-        <v>60</v>
+        <v>685</v>
       </c>
       <c r="T7" t="s">
         <v>27</v>
@@ -7151,34 +7190,40 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>678</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>679</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F8">
+        <v>46095</v>
       </c>
       <c r="G8" s="1">
-        <v>46072</v>
+        <v>46041</v>
+      </c>
+      <c r="H8" s="1">
+        <v>46095</v>
       </c>
       <c r="I8" t="s">
         <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="L8">
-        <v>12182961764</v>
+        <v>12176904334</v>
       </c>
       <c r="M8">
-        <v>332112527</v>
+        <v>326894195</v>
       </c>
       <c r="N8" t="s">
         <v>27</v>
@@ -7187,16 +7232,16 @@
         <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>64</v>
+        <v>680</v>
       </c>
       <c r="Q8" t="s">
         <v>27</v>
       </c>
       <c r="R8" s="1">
-        <v>28801</v>
+        <v>27164</v>
       </c>
       <c r="S8" t="s">
-        <v>65</v>
+        <v>681</v>
       </c>
       <c r="T8" t="s">
         <v>27</v>
@@ -7204,10 +7249,10 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>667</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>668</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -7216,22 +7261,25 @@
         <v>23</v>
       </c>
       <c r="G9" s="1">
-        <v>46055</v>
+        <v>46077</v>
+      </c>
+      <c r="H9" s="1">
+        <v>46094</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>669</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>670</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L9">
-        <v>12178154519</v>
+        <v>12175735121</v>
       </c>
       <c r="M9">
-        <v>328809730</v>
+        <v>325474346</v>
       </c>
       <c r="N9" t="s">
         <v>27</v>
@@ -7240,16 +7288,16 @@
         <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>68</v>
+        <v>671</v>
       </c>
       <c r="Q9" t="s">
         <v>27</v>
       </c>
       <c r="R9" s="1">
-        <v>31852</v>
+        <v>31397</v>
       </c>
       <c r="S9" t="s">
-        <v>69</v>
+        <v>672</v>
       </c>
       <c r="T9" t="s">
         <v>27</v>
@@ -7257,34 +7305,34 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>673</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>674</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>675</v>
       </c>
       <c r="G10" s="1">
-        <v>45896</v>
+        <v>46077</v>
+      </c>
+      <c r="H10" s="1">
+        <v>46094</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>669</v>
       </c>
       <c r="J10" t="s">
-        <v>72</v>
+        <v>670</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10">
-        <v>12179704727</v>
+        <v>47</v>
       </c>
       <c r="M10">
-        <v>331091437</v>
+        <v>332509311</v>
       </c>
       <c r="N10" t="s">
         <v>27</v>
@@ -7293,16 +7341,16 @@
         <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>73</v>
+        <v>676</v>
       </c>
       <c r="Q10" t="s">
         <v>27</v>
       </c>
       <c r="R10" s="1">
-        <v>35154</v>
+        <v>34195</v>
       </c>
       <c r="S10" t="s">
-        <v>74</v>
+        <v>677</v>
       </c>
       <c r="T10" t="s">
         <v>27</v>
@@ -7310,34 +7358,40 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>663</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>664</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F11">
+        <v>46092</v>
       </c>
       <c r="G11" s="1">
-        <v>46055</v>
+        <v>46035</v>
+      </c>
+      <c r="H11" s="1">
+        <v>46092</v>
       </c>
       <c r="I11" t="s">
         <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>282</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="L11">
-        <v>12179459063</v>
+        <v>12179725003</v>
       </c>
       <c r="M11">
-        <v>330543911</v>
+        <v>331296845</v>
       </c>
       <c r="N11" t="s">
         <v>27</v>
@@ -7346,16 +7400,16 @@
         <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>77</v>
+        <v>665</v>
       </c>
       <c r="Q11" t="s">
         <v>27</v>
       </c>
       <c r="R11" s="1">
-        <v>30630</v>
+        <v>27282</v>
       </c>
       <c r="S11" t="s">
-        <v>78</v>
+        <v>666</v>
       </c>
       <c r="T11" t="s">
         <v>27</v>
@@ -7363,37 +7417,40 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>649</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>650</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12">
-        <v>46112</v>
+        <v>630</v>
+      </c>
+      <c r="F12">
+        <v>46091</v>
       </c>
       <c r="G12" s="1">
-        <v>46111</v>
+        <v>46030</v>
+      </c>
+      <c r="H12" s="1">
+        <v>46091</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="K12" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="L12">
-        <v>12183528166</v>
+        <v>12177520975</v>
       </c>
       <c r="M12">
-        <v>332283054</v>
+        <v>327472006</v>
       </c>
       <c r="N12" t="s">
         <v>27</v>
@@ -7402,16 +7459,16 @@
         <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
       </c>
       <c r="R12" s="1">
-        <v>24591</v>
+        <v>29451</v>
       </c>
       <c r="S12" t="s">
-        <v>83</v>
+        <v>652</v>
       </c>
       <c r="T12" t="s">
         <v>27</v>
@@ -7419,34 +7476,40 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>653</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>654</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F13">
+        <v>46091</v>
       </c>
       <c r="G13" s="1">
-        <v>46071</v>
+        <v>45931</v>
+      </c>
+      <c r="H13" s="1">
+        <v>46091</v>
       </c>
       <c r="I13" t="s">
         <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>86</v>
+        <v>255</v>
       </c>
       <c r="K13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L13">
-        <v>12087775022</v>
+        <v>12173757775</v>
       </c>
       <c r="M13">
-        <v>307442675</v>
+        <v>323169481</v>
       </c>
       <c r="N13" t="s">
         <v>27</v>
@@ -7455,16 +7518,16 @@
         <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>87</v>
+        <v>655</v>
       </c>
       <c r="Q13" t="s">
         <v>27</v>
       </c>
       <c r="R13" s="1">
-        <v>32166</v>
+        <v>31807</v>
       </c>
       <c r="S13" t="s">
-        <v>88</v>
+        <v>656</v>
       </c>
       <c r="T13" t="s">
         <v>27</v>
@@ -7472,34 +7535,40 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>657</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>658</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F14">
+        <v>46091</v>
       </c>
       <c r="G14" s="1">
-        <v>46058</v>
+        <v>46076</v>
+      </c>
+      <c r="H14" s="1">
+        <v>46091</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J14" t="s">
-        <v>25</v>
+        <v>659</v>
       </c>
       <c r="K14" t="s">
-        <v>91</v>
+        <v>660</v>
       </c>
       <c r="L14">
-        <v>12178082616</v>
+        <v>12181820012</v>
       </c>
       <c r="M14">
-        <v>328321095</v>
+        <v>33456465</v>
       </c>
       <c r="N14" t="s">
         <v>27</v>
@@ -7508,16 +7577,16 @@
         <v>27</v>
       </c>
       <c r="P14" t="s">
-        <v>92</v>
+        <v>661</v>
       </c>
       <c r="Q14" t="s">
         <v>27</v>
       </c>
       <c r="R14" s="1">
-        <v>32983</v>
+        <v>27200</v>
       </c>
       <c r="S14" t="s">
-        <v>93</v>
+        <v>662</v>
       </c>
       <c r="T14" t="s">
         <v>27</v>
@@ -7525,34 +7594,40 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>641</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>642</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F15">
+        <v>46090</v>
       </c>
       <c r="G15" s="1">
-        <v>45945</v>
+        <v>46055</v>
+      </c>
+      <c r="H15" s="1">
+        <v>46090</v>
       </c>
       <c r="I15" t="s">
         <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="L15">
-        <v>12179664043</v>
+        <v>12182162759</v>
       </c>
       <c r="M15">
-        <v>331291410</v>
+        <v>334874181</v>
       </c>
       <c r="N15" t="s">
         <v>27</v>
@@ -7561,16 +7636,16 @@
         <v>27</v>
       </c>
       <c r="P15" t="s">
-        <v>96</v>
+        <v>643</v>
       </c>
       <c r="Q15" t="s">
         <v>27</v>
       </c>
       <c r="R15" s="1">
-        <v>33941</v>
+        <v>33972</v>
       </c>
       <c r="S15" t="s">
-        <v>97</v>
+        <v>644</v>
       </c>
       <c r="T15" t="s">
         <v>27</v>
@@ -7578,34 +7653,40 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>645</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>646</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F16">
+        <v>46090</v>
       </c>
       <c r="G16" s="1">
-        <v>45942</v>
+        <v>46055</v>
+      </c>
+      <c r="H16" s="1">
+        <v>46090</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="L16">
-        <v>12181124116</v>
+        <v>12182029339</v>
       </c>
       <c r="M16">
-        <v>332929027</v>
+        <v>332535398</v>
       </c>
       <c r="N16" t="s">
         <v>27</v>
@@ -7614,16 +7695,16 @@
         <v>27</v>
       </c>
       <c r="P16" t="s">
-        <v>101</v>
+        <v>647</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
       </c>
       <c r="R16" s="1">
-        <v>29877</v>
+        <v>29437</v>
       </c>
       <c r="S16" t="s">
-        <v>102</v>
+        <v>648</v>
       </c>
       <c r="T16" t="s">
         <v>27</v>
@@ -7631,34 +7712,40 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>633</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>634</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F17">
+        <v>46087</v>
       </c>
       <c r="G17" s="1">
-        <v>46109</v>
+        <v>46076</v>
+      </c>
+      <c r="H17" s="1">
+        <v>46087</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J17" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="K17" t="s">
         <v>47</v>
       </c>
       <c r="L17">
-        <v>12078228209</v>
+        <v>12179964579</v>
       </c>
       <c r="M17">
-        <v>298827166</v>
+        <v>331659352</v>
       </c>
       <c r="N17" t="s">
         <v>27</v>
@@ -7667,16 +7754,16 @@
         <v>27</v>
       </c>
       <c r="P17" t="s">
-        <v>105</v>
+        <v>635</v>
       </c>
       <c r="Q17" t="s">
         <v>27</v>
       </c>
       <c r="R17" s="1">
-        <v>32714</v>
+        <v>30525</v>
       </c>
       <c r="S17" t="s">
-        <v>106</v>
+        <v>636</v>
       </c>
       <c r="T17" t="s">
         <v>27</v>
@@ -7684,34 +7771,40 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>637</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>638</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F18">
+        <v>46087</v>
       </c>
       <c r="G18" s="1">
-        <v>46055</v>
+        <v>45931</v>
+      </c>
+      <c r="H18" s="1">
+        <v>46087</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J18" t="s">
-        <v>109</v>
+        <v>255</v>
       </c>
       <c r="K18" t="s">
-        <v>110</v>
+        <v>337</v>
       </c>
       <c r="L18">
-        <v>12178308562</v>
+        <v>12176565967</v>
       </c>
       <c r="M18">
-        <v>329256360</v>
+        <v>326546413</v>
       </c>
       <c r="N18" t="s">
         <v>27</v>
@@ -7720,16 +7813,16 @@
         <v>27</v>
       </c>
       <c r="P18" t="s">
-        <v>111</v>
+        <v>639</v>
       </c>
       <c r="Q18" t="s">
         <v>27</v>
       </c>
       <c r="R18" s="1">
-        <v>29611</v>
+        <v>29726</v>
       </c>
       <c r="S18" t="s">
-        <v>112</v>
+        <v>640</v>
       </c>
       <c r="T18" t="s">
         <v>27</v>
@@ -7737,34 +7830,40 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>627</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>628</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>629</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>630</v>
+      </c>
+      <c r="F19">
+        <v>46084</v>
       </c>
       <c r="G19" s="1">
-        <v>46118</v>
+        <v>45931</v>
+      </c>
+      <c r="H19" s="1">
+        <v>46084</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J19" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="K19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L19">
-        <v>12182936079</v>
+        <v>12176457795</v>
       </c>
       <c r="M19">
-        <v>335360181</v>
+        <v>326398414</v>
       </c>
       <c r="N19" t="s">
         <v>27</v>
@@ -7773,16 +7872,16 @@
         <v>27</v>
       </c>
       <c r="P19" t="s">
-        <v>115</v>
+        <v>631</v>
       </c>
       <c r="Q19" t="s">
         <v>27</v>
       </c>
       <c r="R19" s="1">
-        <v>32483</v>
+        <v>31109</v>
       </c>
       <c r="S19" t="s">
-        <v>116</v>
+        <v>632</v>
       </c>
       <c r="T19" t="s">
         <v>27</v>
@@ -7790,10 +7889,10 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -7802,22 +7901,22 @@
         <v>23</v>
       </c>
       <c r="G20" s="1">
-        <v>46048</v>
+        <v>46058</v>
       </c>
       <c r="I20" t="s">
         <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="L20">
-        <v>12182776594</v>
+        <v>12178088103</v>
       </c>
       <c r="M20">
-        <v>334041139</v>
+        <v>328500771</v>
       </c>
       <c r="N20" t="s">
         <v>27</v>
@@ -7826,16 +7925,16 @@
         <v>27</v>
       </c>
       <c r="P20" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
       </c>
       <c r="R20" s="1">
-        <v>36094</v>
+        <v>32840</v>
       </c>
       <c r="S20" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="T20" t="s">
         <v>27</v>
@@ -7843,10 +7942,10 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -7855,22 +7954,22 @@
         <v>23</v>
       </c>
       <c r="G21" s="1">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="I21" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L21">
-        <v>12176457567</v>
+        <v>12175808930</v>
       </c>
       <c r="M21">
-        <v>326408274</v>
+        <v>325619565</v>
       </c>
       <c r="N21" t="s">
         <v>27</v>
@@ -7879,16 +7978,16 @@
         <v>27</v>
       </c>
       <c r="P21" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
       </c>
       <c r="R21" s="1">
-        <v>33702</v>
+        <v>31010</v>
       </c>
       <c r="S21" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
         <v>27</v>
@@ -7896,10 +7995,10 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -7908,22 +8007,22 @@
         <v>23</v>
       </c>
       <c r="G22" s="1">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J22" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="K22" t="s">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="L22">
-        <v>12182370687</v>
+        <v>12182289961</v>
       </c>
       <c r="M22">
-        <v>335233201</v>
+        <v>332901890</v>
       </c>
       <c r="N22" t="s">
         <v>27</v>
@@ -7932,16 +8031,16 @@
         <v>27</v>
       </c>
       <c r="P22" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="Q22" t="s">
         <v>27</v>
       </c>
       <c r="R22" s="1">
-        <v>34550</v>
+        <v>25787</v>
       </c>
       <c r="S22" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="T22" t="s">
         <v>27</v>
@@ -7949,10 +8048,10 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -7961,22 +8060,22 @@
         <v>23</v>
       </c>
       <c r="G23" s="1">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="I23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="K23" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L23">
-        <v>12172971340</v>
+        <v>12173759107</v>
       </c>
       <c r="M23">
-        <v>322387981</v>
+        <v>323401384</v>
       </c>
       <c r="N23" t="s">
         <v>27</v>
@@ -7985,16 +8084,16 @@
         <v>27</v>
       </c>
       <c r="P23" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="Q23" t="s">
         <v>27</v>
       </c>
       <c r="R23" s="1">
-        <v>31130</v>
+        <v>34776</v>
       </c>
       <c r="S23" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="T23" t="s">
         <v>27</v>
@@ -8002,10 +8101,10 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
@@ -8014,22 +8113,22 @@
         <v>23</v>
       </c>
       <c r="G24" s="1">
-        <v>46077</v>
+        <v>46051</v>
       </c>
       <c r="I24" t="s">
         <v>24</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="K24" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L24">
-        <v>12181176080</v>
+        <v>12182662607</v>
       </c>
       <c r="M24">
-        <v>332773477</v>
+        <v>335235387</v>
       </c>
       <c r="N24" t="s">
         <v>27</v>
@@ -8038,16 +8137,16 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="Q24" t="s">
         <v>27</v>
       </c>
       <c r="R24" s="1">
-        <v>35198</v>
+        <v>28650</v>
       </c>
       <c r="S24" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="T24" t="s">
         <v>27</v>
@@ -8055,10 +8154,10 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
@@ -8067,22 +8166,22 @@
         <v>23</v>
       </c>
       <c r="G25" s="1">
-        <v>46041</v>
+        <v>45939</v>
       </c>
       <c r="I25" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="K25" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="L25">
-        <v>12175390178</v>
+        <v>12178058560</v>
       </c>
       <c r="M25">
-        <v>325268584</v>
+        <v>328282278</v>
       </c>
       <c r="N25" t="s">
         <v>27</v>
@@ -8091,16 +8190,16 @@
         <v>27</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="Q25" t="s">
         <v>27</v>
       </c>
       <c r="R25" s="1">
-        <v>31538</v>
+        <v>30144</v>
       </c>
       <c r="S25" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="T25" t="s">
         <v>27</v>
@@ -8108,10 +8207,10 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -8120,22 +8219,22 @@
         <v>23</v>
       </c>
       <c r="G26" s="1">
-        <v>46055</v>
+        <v>46072</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J26" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="K26" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L26">
-        <v>12179027131</v>
+        <v>12182961764</v>
       </c>
       <c r="M26">
-        <v>330124552</v>
+        <v>332112527</v>
       </c>
       <c r="N26" t="s">
         <v>27</v>
@@ -8144,16 +8243,16 @@
         <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="Q26" t="s">
         <v>27</v>
       </c>
       <c r="R26" s="1">
-        <v>32584</v>
+        <v>28801</v>
       </c>
       <c r="S26" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="T26" t="s">
         <v>27</v>
@@ -8161,37 +8260,34 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
         <v>23</v>
       </c>
-      <c r="E27">
-        <v>46118</v>
-      </c>
       <c r="G27" s="1">
-        <v>46118</v>
+        <v>46055</v>
       </c>
       <c r="I27" t="s">
         <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K27" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="L27">
-        <v>12176731314</v>
+        <v>12178154519</v>
       </c>
       <c r="M27">
-        <v>326740058</v>
+        <v>328809730</v>
       </c>
       <c r="N27" t="s">
         <v>27</v>
@@ -8200,16 +8296,16 @@
         <v>27</v>
       </c>
       <c r="P27" t="s">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="Q27" t="s">
         <v>27</v>
       </c>
       <c r="R27" s="1">
-        <v>28743</v>
+        <v>31852</v>
       </c>
       <c r="S27" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="T27" t="s">
         <v>27</v>
@@ -8217,10 +8313,10 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
         <v>22</v>
@@ -8229,22 +8325,22 @@
         <v>23</v>
       </c>
       <c r="G28" s="1">
-        <v>45945</v>
+        <v>45896</v>
       </c>
       <c r="I28" t="s">
         <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="K28" t="s">
         <v>34</v>
       </c>
       <c r="L28">
-        <v>12167307101</v>
+        <v>12179704727</v>
       </c>
       <c r="M28">
-        <v>317357700</v>
+        <v>331091437</v>
       </c>
       <c r="N28" t="s">
         <v>27</v>
@@ -8253,16 +8349,16 @@
         <v>27</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="Q28" t="s">
         <v>27</v>
       </c>
       <c r="R28" s="1">
-        <v>35305</v>
+        <v>35154</v>
       </c>
       <c r="S28" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="T28" t="s">
         <v>27</v>
@@ -8270,10 +8366,10 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -8282,22 +8378,22 @@
         <v>23</v>
       </c>
       <c r="G29" s="1">
-        <v>46118</v>
+        <v>46055</v>
       </c>
       <c r="I29" t="s">
         <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="K29" t="s">
         <v>47</v>
       </c>
       <c r="L29">
-        <v>12168469529</v>
+        <v>12179459063</v>
       </c>
       <c r="M29">
-        <v>317290886</v>
+        <v>330543911</v>
       </c>
       <c r="N29" t="s">
         <v>27</v>
@@ -8306,16 +8402,16 @@
         <v>27</v>
       </c>
       <c r="P29" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Q29" t="s">
         <v>27</v>
       </c>
       <c r="R29" s="1">
-        <v>32990</v>
+        <v>30630</v>
       </c>
       <c r="S29" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="T29" t="s">
         <v>27</v>
@@ -8323,10 +8419,10 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
@@ -8334,23 +8430,26 @@
       <c r="D30" t="s">
         <v>23</v>
       </c>
+      <c r="E30">
+        <v>46112</v>
+      </c>
       <c r="G30" s="1">
-        <v>45873</v>
+        <v>46111</v>
       </c>
       <c r="I30" t="s">
         <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L30">
-        <v>12081209545</v>
+        <v>12183528166</v>
       </c>
       <c r="M30">
-        <v>300700130</v>
+        <v>332283054</v>
       </c>
       <c r="N30" t="s">
         <v>27</v>
@@ -8359,16 +8458,16 @@
         <v>27</v>
       </c>
       <c r="P30" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="Q30" t="s">
         <v>27</v>
       </c>
       <c r="R30" s="1">
-        <v>32332</v>
+        <v>24591</v>
       </c>
       <c r="S30" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="T30" t="s">
         <v>27</v>
@@ -8376,10 +8475,10 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
@@ -8388,22 +8487,22 @@
         <v>23</v>
       </c>
       <c r="G31" s="1">
-        <v>46052</v>
+        <v>46071</v>
       </c>
       <c r="I31" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J31" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="L31">
-        <v>12182857380</v>
+        <v>12087775022</v>
       </c>
       <c r="M31">
-        <v>335920489</v>
+        <v>307442675</v>
       </c>
       <c r="N31" t="s">
         <v>27</v>
@@ -8412,16 +8511,16 @@
         <v>27</v>
       </c>
       <c r="P31" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="Q31" t="s">
         <v>27</v>
       </c>
       <c r="R31" s="1">
-        <v>34668</v>
+        <v>32166</v>
       </c>
       <c r="S31" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="T31" t="s">
         <v>27</v>
@@ -8429,10 +8528,10 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
         <v>22</v>
@@ -8441,22 +8540,22 @@
         <v>23</v>
       </c>
       <c r="G32" s="1">
-        <v>46104</v>
+        <v>46058</v>
       </c>
       <c r="I32" t="s">
         <v>24</v>
       </c>
       <c r="J32" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="L32">
-        <v>12178385325</v>
+        <v>12178082616</v>
       </c>
       <c r="M32">
-        <v>329360116</v>
+        <v>328321095</v>
       </c>
       <c r="N32" t="s">
         <v>27</v>
@@ -8465,16 +8564,16 @@
         <v>27</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="Q32" t="s">
         <v>27</v>
       </c>
       <c r="R32" s="1">
-        <v>31970</v>
+        <v>32983</v>
       </c>
       <c r="S32" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="T32" t="s">
         <v>27</v>
@@ -8482,10 +8581,10 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>22</v>
@@ -8494,22 +8593,22 @@
         <v>23</v>
       </c>
       <c r="G33" s="1">
-        <v>46041</v>
+        <v>45945</v>
       </c>
       <c r="I33" t="s">
         <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="K33" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="L33">
-        <v>12181176129</v>
+        <v>12179664043</v>
       </c>
       <c r="M33">
-        <v>333420578</v>
+        <v>331291410</v>
       </c>
       <c r="N33" t="s">
         <v>27</v>
@@ -8518,16 +8617,16 @@
         <v>27</v>
       </c>
       <c r="P33" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="Q33" t="s">
         <v>27</v>
       </c>
       <c r="R33" s="1">
-        <v>29144</v>
+        <v>33941</v>
       </c>
       <c r="S33" t="s">
-        <v>183</v>
+        <v>97</v>
       </c>
       <c r="T33" t="s">
         <v>27</v>
@@ -8535,10 +8634,10 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
         <v>22</v>
@@ -8547,22 +8646,22 @@
         <v>23</v>
       </c>
       <c r="G34" s="1">
-        <v>46041</v>
+        <v>45942</v>
       </c>
       <c r="I34" t="s">
         <v>24</v>
       </c>
       <c r="J34" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="K34" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="L34">
-        <v>12182368406</v>
+        <v>12181124116</v>
       </c>
       <c r="M34">
-        <v>335180485</v>
+        <v>332929027</v>
       </c>
       <c r="N34" t="s">
         <v>27</v>
@@ -8571,16 +8670,16 @@
         <v>27</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>101</v>
       </c>
       <c r="Q34" t="s">
         <v>27</v>
       </c>
       <c r="R34" s="1">
-        <v>28408</v>
+        <v>29877</v>
       </c>
       <c r="S34" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="T34" t="s">
         <v>27</v>
@@ -8588,10 +8687,10 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
@@ -8600,22 +8699,22 @@
         <v>23</v>
       </c>
       <c r="G35" s="1">
-        <v>46041</v>
+        <v>46109</v>
       </c>
       <c r="I35" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s">
         <v>47</v>
       </c>
       <c r="L35">
-        <v>12181435381</v>
+        <v>12078228209</v>
       </c>
       <c r="M35">
-        <v>333124286</v>
+        <v>298827166</v>
       </c>
       <c r="N35" t="s">
         <v>27</v>
@@ -8624,16 +8723,16 @@
         <v>27</v>
       </c>
       <c r="P35" t="s">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="Q35" t="s">
         <v>27</v>
       </c>
       <c r="R35" s="1">
-        <v>32813</v>
+        <v>32714</v>
       </c>
       <c r="S35" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="T35" t="s">
         <v>27</v>
@@ -8641,10 +8740,10 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
         <v>22</v>
@@ -8653,22 +8752,22 @@
         <v>23</v>
       </c>
       <c r="G36" s="1">
-        <v>45938</v>
+        <v>46055</v>
       </c>
       <c r="I36" t="s">
         <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="K36" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L36">
-        <v>12179724626</v>
+        <v>12178308562</v>
       </c>
       <c r="M36">
-        <v>331098245</v>
+        <v>329256360</v>
       </c>
       <c r="N36" t="s">
         <v>27</v>
@@ -8677,16 +8776,16 @@
         <v>27</v>
       </c>
       <c r="P36" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="Q36" t="s">
         <v>27</v>
       </c>
       <c r="R36" s="1">
-        <v>28551</v>
+        <v>29611</v>
       </c>
       <c r="S36" t="s">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="T36" t="s">
         <v>27</v>
@@ -8694,10 +8793,10 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
         <v>22</v>
@@ -8706,22 +8805,22 @@
         <v>23</v>
       </c>
       <c r="G37" s="1">
-        <v>46010</v>
+        <v>46118</v>
       </c>
       <c r="I37" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="K37" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="L37">
-        <v>12179726105</v>
+        <v>12182936079</v>
       </c>
       <c r="M37">
-        <v>331296160</v>
+        <v>335360181</v>
       </c>
       <c r="N37" t="s">
         <v>27</v>
@@ -8730,16 +8829,16 @@
         <v>27</v>
       </c>
       <c r="P37" t="s">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="Q37" t="s">
         <v>27</v>
       </c>
       <c r="R37" s="1">
-        <v>33105</v>
+        <v>32483</v>
       </c>
       <c r="S37" t="s">
-        <v>200</v>
+        <v>116</v>
       </c>
       <c r="T37" t="s">
         <v>27</v>
@@ -8747,10 +8846,10 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
         <v>22</v>
@@ -8759,22 +8858,22 @@
         <v>23</v>
       </c>
       <c r="G38" s="1">
-        <v>46065</v>
+        <v>46048</v>
       </c>
       <c r="I38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J38" t="s">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="L38">
-        <v>12178850279</v>
+        <v>12182776594</v>
       </c>
       <c r="M38">
-        <v>330087754</v>
+        <v>334041139</v>
       </c>
       <c r="N38" t="s">
         <v>27</v>
@@ -8783,16 +8882,16 @@
         <v>27</v>
       </c>
       <c r="P38" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="Q38" t="s">
         <v>27</v>
       </c>
       <c r="R38" s="1">
-        <v>28167</v>
+        <v>36094</v>
       </c>
       <c r="S38" t="s">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="T38" t="s">
         <v>27</v>
@@ -8800,10 +8899,10 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
         <v>22</v>
@@ -8812,22 +8911,22 @@
         <v>23</v>
       </c>
       <c r="G39" s="1">
-        <v>45938</v>
+        <v>45943</v>
       </c>
       <c r="I39" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J39" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="K39" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="L39">
-        <v>12179725011</v>
+        <v>12176457567</v>
       </c>
       <c r="M39">
-        <v>331092069</v>
+        <v>326408274</v>
       </c>
       <c r="N39" t="s">
         <v>27</v>
@@ -8836,16 +8935,16 @@
         <v>27</v>
       </c>
       <c r="P39" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="Q39" t="s">
         <v>27</v>
       </c>
       <c r="R39" s="1">
-        <v>23987</v>
+        <v>33702</v>
       </c>
       <c r="S39" t="s">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="T39" t="s">
         <v>27</v>
@@ -8853,10 +8952,10 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
         <v>22</v>
@@ -8865,7 +8964,7 @@
         <v>23</v>
       </c>
       <c r="G40" s="1">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="I40" t="s">
         <v>32</v>
@@ -8874,13 +8973,13 @@
         <v>129</v>
       </c>
       <c r="K40" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="L40">
-        <v>12179192186</v>
+        <v>12182370687</v>
       </c>
       <c r="M40">
-        <v>330251228</v>
+        <v>335233201</v>
       </c>
       <c r="N40" t="s">
         <v>27</v>
@@ -8889,16 +8988,16 @@
         <v>27</v>
       </c>
       <c r="P40" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="Q40" t="s">
         <v>27</v>
       </c>
       <c r="R40" s="1">
-        <v>31693</v>
+        <v>34550</v>
       </c>
       <c r="S40" t="s">
-        <v>213</v>
+        <v>132</v>
       </c>
       <c r="T40" t="s">
         <v>27</v>
@@ -8906,10 +9005,10 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
@@ -8918,22 +9017,22 @@
         <v>23</v>
       </c>
       <c r="G41" s="1">
-        <v>46056</v>
+        <v>46076</v>
       </c>
       <c r="I41" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="K41" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="L41">
-        <v>12179775545</v>
+        <v>12172971340</v>
       </c>
       <c r="M41">
-        <v>331063751</v>
+        <v>322387981</v>
       </c>
       <c r="N41" t="s">
         <v>27</v>
@@ -8942,16 +9041,16 @@
         <v>27</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>136</v>
       </c>
       <c r="Q41" t="s">
         <v>27</v>
       </c>
       <c r="R41" s="1">
-        <v>27859</v>
+        <v>31130</v>
       </c>
       <c r="S41" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="T41" t="s">
         <v>27</v>
@@ -8959,10 +9058,10 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="B42" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
         <v>22</v>
@@ -8971,22 +9070,22 @@
         <v>23</v>
       </c>
       <c r="G42" s="1">
-        <v>46051</v>
+        <v>46077</v>
       </c>
       <c r="I42" t="s">
         <v>24</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="K42" t="s">
         <v>47</v>
       </c>
       <c r="L42">
-        <v>12181922396</v>
+        <v>12181176080</v>
       </c>
       <c r="M42">
-        <v>332649008</v>
+        <v>332773477</v>
       </c>
       <c r="N42" t="s">
         <v>27</v>
@@ -8995,16 +9094,16 @@
         <v>27</v>
       </c>
       <c r="P42" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="Q42" t="s">
         <v>27</v>
       </c>
       <c r="R42" s="1">
-        <v>32509</v>
+        <v>35198</v>
       </c>
       <c r="S42" t="s">
-        <v>223</v>
+        <v>142</v>
       </c>
       <c r="T42" t="s">
         <v>27</v>
@@ -9012,10 +9111,10 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="B43" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
         <v>22</v>
@@ -9024,22 +9123,22 @@
         <v>23</v>
       </c>
       <c r="G43" s="1">
-        <v>46028</v>
+        <v>46041</v>
       </c>
       <c r="I43" t="s">
         <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K43" t="s">
         <v>47</v>
       </c>
       <c r="L43">
-        <v>12179739373</v>
+        <v>12175390178</v>
       </c>
       <c r="M43">
-        <v>331092166</v>
+        <v>325268584</v>
       </c>
       <c r="N43" t="s">
         <v>27</v>
@@ -9048,16 +9147,16 @@
         <v>27</v>
       </c>
       <c r="P43" t="s">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="Q43" t="s">
         <v>27</v>
       </c>
       <c r="R43" s="1">
-        <v>24160</v>
+        <v>31538</v>
       </c>
       <c r="S43" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="T43" t="s">
         <v>27</v>
@@ -9065,10 +9164,10 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>228</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
-        <v>229</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
         <v>22</v>
@@ -9077,22 +9176,22 @@
         <v>23</v>
       </c>
       <c r="G44" s="1">
-        <v>46108</v>
+        <v>46055</v>
       </c>
       <c r="I44" t="s">
         <v>32</v>
       </c>
       <c r="J44" t="s">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="K44" t="s">
         <v>34</v>
       </c>
       <c r="L44">
-        <v>12089974079</v>
+        <v>12179027131</v>
       </c>
       <c r="M44">
-        <v>310451663</v>
+        <v>330124552</v>
       </c>
       <c r="N44" t="s">
         <v>27</v>
@@ -9101,16 +9200,16 @@
         <v>27</v>
       </c>
       <c r="P44" t="s">
-        <v>231</v>
+        <v>151</v>
       </c>
       <c r="Q44" t="s">
         <v>27</v>
       </c>
       <c r="R44" s="1">
-        <v>33980</v>
+        <v>32584</v>
       </c>
       <c r="S44" t="s">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="T44" t="s">
         <v>27</v>
@@ -9118,34 +9217,37 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="B45" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
         <v>23</v>
       </c>
+      <c r="E45">
+        <v>46118</v>
+      </c>
       <c r="G45" s="1">
-        <v>46055</v>
+        <v>46118</v>
       </c>
       <c r="I45" t="s">
         <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="K45" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="L45">
-        <v>12179044849</v>
+        <v>12176731314</v>
       </c>
       <c r="M45">
-        <v>330075799</v>
+        <v>326740058</v>
       </c>
       <c r="N45" t="s">
         <v>27</v>
@@ -9154,16 +9256,16 @@
         <v>27</v>
       </c>
       <c r="P45" t="s">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="Q45" t="s">
         <v>27</v>
       </c>
       <c r="R45" s="1">
-        <v>27165</v>
+        <v>28743</v>
       </c>
       <c r="S45" t="s">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="T45" t="s">
         <v>27</v>
@@ -9171,10 +9273,10 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>237</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s">
-        <v>238</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
         <v>22</v>
@@ -9183,22 +9285,22 @@
         <v>23</v>
       </c>
       <c r="G46" s="1">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="I46" t="s">
         <v>32</v>
       </c>
       <c r="J46" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K46" t="s">
         <v>34</v>
       </c>
       <c r="L46">
-        <v>12179739349</v>
+        <v>12167307101</v>
       </c>
       <c r="M46">
-        <v>331076535</v>
+        <v>317357700</v>
       </c>
       <c r="N46" t="s">
         <v>27</v>
@@ -9207,16 +9309,16 @@
         <v>27</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>161</v>
       </c>
       <c r="Q46" t="s">
         <v>27</v>
       </c>
       <c r="R46" s="1">
-        <v>33573</v>
+        <v>35305</v>
       </c>
       <c r="S46" t="s">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="T46" t="s">
         <v>27</v>
@@ -9224,10 +9326,10 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
         <v>22</v>
@@ -9236,22 +9338,22 @@
         <v>23</v>
       </c>
       <c r="G47" s="1">
-        <v>46070</v>
+        <v>46118</v>
       </c>
       <c r="I47" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J47" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s">
         <v>47</v>
       </c>
       <c r="L47">
-        <v>12181747446</v>
+        <v>12168469529</v>
       </c>
       <c r="M47">
-        <v>333014880</v>
+        <v>317290886</v>
       </c>
       <c r="N47" t="s">
         <v>27</v>
@@ -9260,16 +9362,16 @@
         <v>27</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="Q47" t="s">
         <v>27</v>
       </c>
       <c r="R47" s="1">
-        <v>30064</v>
+        <v>32990</v>
       </c>
       <c r="S47" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="T47" t="s">
         <v>27</v>
@@ -9277,10 +9379,10 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="C48" t="s">
         <v>22</v>
@@ -9289,22 +9391,22 @@
         <v>23</v>
       </c>
       <c r="G48" s="1">
-        <v>46055</v>
+        <v>45873</v>
       </c>
       <c r="I48" t="s">
         <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="K48" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L48">
-        <v>12174925624</v>
+        <v>12081209545</v>
       </c>
       <c r="M48">
-        <v>324698070</v>
+        <v>300700130</v>
       </c>
       <c r="N48" t="s">
         <v>27</v>
@@ -9313,16 +9415,16 @@
         <v>27</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="Q48" t="s">
         <v>27</v>
       </c>
       <c r="R48" s="1">
-        <v>31470</v>
+        <v>32332</v>
       </c>
       <c r="S48" t="s">
-        <v>248</v>
+        <v>171</v>
       </c>
       <c r="T48" t="s">
         <v>27</v>
@@ -9330,10 +9432,10 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>249</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
         <v>22</v>
@@ -9342,22 +9444,22 @@
         <v>23</v>
       </c>
       <c r="G49" s="1">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="I49" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>216</v>
+        <v>46</v>
       </c>
       <c r="K49" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L49">
-        <v>12179664378</v>
+        <v>12182857380</v>
       </c>
       <c r="M49">
-        <v>331225549</v>
+        <v>335920489</v>
       </c>
       <c r="N49" t="s">
         <v>27</v>
@@ -9366,16 +9468,16 @@
         <v>27</v>
       </c>
       <c r="P49" t="s">
-        <v>251</v>
+        <v>174</v>
       </c>
       <c r="Q49" t="s">
         <v>27</v>
       </c>
       <c r="R49" s="1">
-        <v>28805</v>
+        <v>34668</v>
       </c>
       <c r="S49" t="s">
-        <v>252</v>
+        <v>175</v>
       </c>
       <c r="T49" t="s">
         <v>27</v>
@@ -9383,10 +9485,10 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s">
         <v>22</v>
@@ -9395,22 +9497,22 @@
         <v>23</v>
       </c>
       <c r="G50" s="1">
-        <v>46042</v>
+        <v>46104</v>
       </c>
       <c r="I50" t="s">
         <v>24</v>
       </c>
       <c r="J50" t="s">
-        <v>255</v>
+        <v>119</v>
       </c>
       <c r="K50" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="L50">
-        <v>12179744347</v>
+        <v>12178385325</v>
       </c>
       <c r="M50">
-        <v>331317052</v>
+        <v>329360116</v>
       </c>
       <c r="N50" t="s">
         <v>27</v>
@@ -9419,16 +9521,16 @@
         <v>27</v>
       </c>
       <c r="P50" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="Q50" t="s">
         <v>27</v>
       </c>
       <c r="R50" s="1">
-        <v>29205</v>
+        <v>31970</v>
       </c>
       <c r="S50" t="s">
-        <v>257</v>
+        <v>179</v>
       </c>
       <c r="T50" t="s">
         <v>27</v>
@@ -9436,10 +9538,10 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="C51" t="s">
         <v>22</v>
@@ -9448,22 +9550,22 @@
         <v>23</v>
       </c>
       <c r="G51" s="1">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="I51" t="s">
         <v>32</v>
       </c>
       <c r="J51" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="K51" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="L51">
-        <v>12178112452</v>
+        <v>12181176129</v>
       </c>
       <c r="M51">
-        <v>328342688</v>
+        <v>333420578</v>
       </c>
       <c r="N51" t="s">
         <v>27</v>
@@ -9472,16 +9574,16 @@
         <v>27</v>
       </c>
       <c r="P51" t="s">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="Q51" t="s">
         <v>27</v>
       </c>
       <c r="R51" s="1">
-        <v>32666</v>
+        <v>29144</v>
       </c>
       <c r="S51" t="s">
-        <v>261</v>
+        <v>183</v>
       </c>
       <c r="T51" t="s">
         <v>27</v>
@@ -9489,10 +9591,10 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>262</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c r="C52" t="s">
         <v>22</v>
@@ -9501,22 +9603,22 @@
         <v>23</v>
       </c>
       <c r="G52" s="1">
-        <v>46104</v>
+        <v>46041</v>
       </c>
       <c r="I52" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J52" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="L52">
-        <v>12079006901</v>
+        <v>12182368406</v>
       </c>
       <c r="M52">
-        <v>299820505</v>
+        <v>335180485</v>
       </c>
       <c r="N52" t="s">
         <v>27</v>
@@ -9525,16 +9627,16 @@
         <v>27</v>
       </c>
       <c r="P52" t="s">
-        <v>264</v>
+        <v>186</v>
       </c>
       <c r="Q52" t="s">
         <v>27</v>
       </c>
       <c r="R52" s="1">
-        <v>35433</v>
+        <v>28408</v>
       </c>
       <c r="S52" t="s">
-        <v>265</v>
+        <v>187</v>
       </c>
       <c r="T52" t="s">
         <v>27</v>
@@ -9542,10 +9644,10 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="C53" t="s">
         <v>22</v>
@@ -9554,22 +9656,22 @@
         <v>23</v>
       </c>
       <c r="G53" s="1">
-        <v>46056</v>
+        <v>46041</v>
       </c>
       <c r="I53" t="s">
         <v>24</v>
       </c>
       <c r="J53" t="s">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="K53" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L53">
-        <v>12178632699</v>
+        <v>12181435381</v>
       </c>
       <c r="M53">
-        <v>329648357</v>
+        <v>333124286</v>
       </c>
       <c r="N53" t="s">
         <v>27</v>
@@ -9578,16 +9680,16 @@
         <v>27</v>
       </c>
       <c r="P53" t="s">
-        <v>269</v>
+        <v>190</v>
       </c>
       <c r="Q53" t="s">
         <v>27</v>
       </c>
       <c r="R53" s="1">
-        <v>27183</v>
+        <v>32813</v>
       </c>
       <c r="S53" t="s">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="T53" t="s">
         <v>27</v>
@@ -9595,10 +9697,10 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>271</v>
+        <v>192</v>
       </c>
       <c r="B54" t="s">
-        <v>272</v>
+        <v>193</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
@@ -9607,22 +9709,22 @@
         <v>23</v>
       </c>
       <c r="G54" s="1">
-        <v>46052</v>
+        <v>45938</v>
       </c>
       <c r="I54" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J54" t="s">
-        <v>273</v>
+        <v>46</v>
       </c>
       <c r="K54" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="L54">
-        <v>12181598757</v>
+        <v>12179724626</v>
       </c>
       <c r="M54">
-        <v>334281130</v>
+        <v>331098245</v>
       </c>
       <c r="N54" t="s">
         <v>27</v>
@@ -9631,16 +9733,16 @@
         <v>27</v>
       </c>
       <c r="P54" t="s">
-        <v>274</v>
+        <v>194</v>
       </c>
       <c r="Q54" t="s">
         <v>27</v>
       </c>
       <c r="R54" s="1">
-        <v>28197</v>
+        <v>28551</v>
       </c>
       <c r="S54" t="s">
-        <v>275</v>
+        <v>195</v>
       </c>
       <c r="T54" t="s">
         <v>27</v>
@@ -9648,10 +9750,10 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="B55" t="s">
-        <v>277</v>
+        <v>197</v>
       </c>
       <c r="C55" t="s">
         <v>22</v>
@@ -9660,22 +9762,22 @@
         <v>23</v>
       </c>
       <c r="G55" s="1">
-        <v>45939</v>
+        <v>46010</v>
       </c>
       <c r="I55" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J55" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="K55" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="L55">
-        <v>12176828161</v>
+        <v>12179726105</v>
       </c>
       <c r="M55">
-        <v>326856609</v>
+        <v>331296160</v>
       </c>
       <c r="N55" t="s">
         <v>27</v>
@@ -9684,16 +9786,16 @@
         <v>27</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="Q55" t="s">
         <v>27</v>
       </c>
       <c r="R55" s="1">
-        <v>31702</v>
+        <v>33105</v>
       </c>
       <c r="S55" t="s">
-        <v>279</v>
+        <v>200</v>
       </c>
       <c r="T55" t="s">
         <v>27</v>
@@ -9701,10 +9803,10 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
         <v>22</v>
@@ -9713,22 +9815,22 @@
         <v>23</v>
       </c>
       <c r="G56" s="1">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="I56" t="s">
         <v>32</v>
       </c>
       <c r="J56" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="K56" t="s">
-        <v>283</v>
+        <v>47</v>
       </c>
       <c r="L56">
-        <v>12181966542</v>
+        <v>12178850279</v>
       </c>
       <c r="M56">
-        <v>334529387</v>
+        <v>330087754</v>
       </c>
       <c r="N56" t="s">
         <v>27</v>
@@ -9737,16 +9839,16 @@
         <v>27</v>
       </c>
       <c r="P56" t="s">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="Q56" t="s">
         <v>27</v>
       </c>
       <c r="R56" s="1">
-        <v>32610</v>
+        <v>28167</v>
       </c>
       <c r="S56" t="s">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="T56" t="s">
         <v>27</v>
@@ -9754,10 +9856,10 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>286</v>
+        <v>206</v>
       </c>
       <c r="B57" t="s">
-        <v>287</v>
+        <v>207</v>
       </c>
       <c r="C57" t="s">
         <v>22</v>
@@ -9766,22 +9868,22 @@
         <v>23</v>
       </c>
       <c r="G57" s="1">
-        <v>45931</v>
+        <v>45938</v>
       </c>
       <c r="I57" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J57" t="s">
-        <v>255</v>
+        <v>46</v>
       </c>
       <c r="K57" t="s">
-        <v>288</v>
+        <v>120</v>
       </c>
       <c r="L57">
-        <v>12163300700</v>
+        <v>12179725011</v>
       </c>
       <c r="M57">
-        <v>315756845</v>
+        <v>331092069</v>
       </c>
       <c r="N57" t="s">
         <v>27</v>
@@ -9790,16 +9892,16 @@
         <v>27</v>
       </c>
       <c r="P57" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="Q57" t="s">
         <v>27</v>
       </c>
       <c r="R57" s="1">
-        <v>29062</v>
+        <v>23987</v>
       </c>
       <c r="S57" t="s">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="T57" t="s">
         <v>27</v>
@@ -9807,10 +9909,10 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="B58" t="s">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="C58" t="s">
         <v>22</v>
@@ -9819,22 +9921,22 @@
         <v>23</v>
       </c>
       <c r="G58" s="1">
-        <v>46041</v>
+        <v>46055</v>
       </c>
       <c r="I58" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J58" t="s">
-        <v>293</v>
+        <v>129</v>
       </c>
       <c r="K58" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="L58">
-        <v>12182503362</v>
+        <v>12179192186</v>
       </c>
       <c r="M58">
-        <v>332775160</v>
+        <v>330251228</v>
       </c>
       <c r="N58" t="s">
         <v>27</v>
@@ -9843,16 +9945,16 @@
         <v>27</v>
       </c>
       <c r="P58" t="s">
-        <v>294</v>
+        <v>212</v>
       </c>
       <c r="Q58" t="s">
         <v>27</v>
       </c>
       <c r="R58" s="1">
-        <v>29192</v>
+        <v>31693</v>
       </c>
       <c r="S58" t="s">
-        <v>295</v>
+        <v>213</v>
       </c>
       <c r="T58" t="s">
         <v>27</v>
@@ -9860,10 +9962,10 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>296</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s">
-        <v>297</v>
+        <v>215</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
@@ -9872,22 +9974,22 @@
         <v>23</v>
       </c>
       <c r="G59" s="1">
-        <v>45932</v>
+        <v>46056</v>
       </c>
       <c r="I59" t="s">
         <v>24</v>
       </c>
       <c r="J59" t="s">
-        <v>298</v>
+        <v>216</v>
       </c>
       <c r="K59" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="L59">
-        <v>12173783651</v>
+        <v>12179775545</v>
       </c>
       <c r="M59">
-        <v>323430333</v>
+        <v>331063751</v>
       </c>
       <c r="N59" t="s">
         <v>27</v>
@@ -9896,16 +9998,16 @@
         <v>27</v>
       </c>
       <c r="P59" t="s">
-        <v>299</v>
+        <v>217</v>
       </c>
       <c r="Q59" t="s">
         <v>27</v>
       </c>
       <c r="R59" s="1">
-        <v>25998</v>
+        <v>27859</v>
       </c>
       <c r="S59" t="s">
-        <v>300</v>
+        <v>218</v>
       </c>
       <c r="T59" t="s">
         <v>27</v>
@@ -9913,10 +10015,10 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>301</v>
+        <v>219</v>
       </c>
       <c r="B60" t="s">
-        <v>302</v>
+        <v>220</v>
       </c>
       <c r="C60" t="s">
         <v>22</v>
@@ -9925,22 +10027,22 @@
         <v>23</v>
       </c>
       <c r="G60" s="1">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="I60" t="s">
         <v>24</v>
       </c>
       <c r="J60" t="s">
-        <v>303</v>
+        <v>221</v>
       </c>
       <c r="K60" t="s">
         <v>47</v>
       </c>
       <c r="L60">
-        <v>12182792370</v>
+        <v>12181922396</v>
       </c>
       <c r="M60">
-        <v>335824293</v>
+        <v>332649008</v>
       </c>
       <c r="N60" t="s">
         <v>27</v>
@@ -9949,16 +10051,16 @@
         <v>27</v>
       </c>
       <c r="P60" t="s">
-        <v>304</v>
+        <v>222</v>
       </c>
       <c r="Q60" t="s">
         <v>27</v>
       </c>
       <c r="R60" s="1">
-        <v>31157</v>
+        <v>32509</v>
       </c>
       <c r="S60" t="s">
-        <v>305</v>
+        <v>223</v>
       </c>
       <c r="T60" t="s">
         <v>27</v>
@@ -9966,10 +10068,10 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>306</v>
+        <v>224</v>
       </c>
       <c r="B61" t="s">
-        <v>307</v>
+        <v>225</v>
       </c>
       <c r="C61" t="s">
         <v>22</v>
@@ -9978,22 +10080,22 @@
         <v>23</v>
       </c>
       <c r="G61" s="1">
-        <v>46056</v>
+        <v>46028</v>
       </c>
       <c r="I61" t="s">
         <v>24</v>
       </c>
       <c r="J61" t="s">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="K61" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L61">
-        <v>12178109682</v>
+        <v>12179739373</v>
       </c>
       <c r="M61">
-        <v>328346098</v>
+        <v>331092166</v>
       </c>
       <c r="N61" t="s">
         <v>27</v>
@@ -10002,16 +10104,16 @@
         <v>27</v>
       </c>
       <c r="P61" t="s">
-        <v>308</v>
+        <v>226</v>
       </c>
       <c r="Q61" t="s">
         <v>27</v>
       </c>
       <c r="R61" s="1">
-        <v>30162</v>
+        <v>24160</v>
       </c>
       <c r="S61" t="s">
-        <v>309</v>
+        <v>227</v>
       </c>
       <c r="T61" t="s">
         <v>27</v>
@@ -10019,10 +10121,10 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>310</v>
+        <v>228</v>
       </c>
       <c r="B62" t="s">
-        <v>311</v>
+        <v>229</v>
       </c>
       <c r="C62" t="s">
         <v>22</v>
@@ -10031,22 +10133,22 @@
         <v>23</v>
       </c>
       <c r="G62" s="1">
-        <v>46052</v>
+        <v>46108</v>
       </c>
       <c r="I62" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J62" t="s">
-        <v>312</v>
+        <v>230</v>
       </c>
       <c r="K62" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="L62">
-        <v>12176592856</v>
+        <v>12089974079</v>
       </c>
       <c r="M62">
-        <v>326550992</v>
+        <v>310451663</v>
       </c>
       <c r="N62" t="s">
         <v>27</v>
@@ -10055,16 +10157,16 @@
         <v>27</v>
       </c>
       <c r="P62" t="s">
-        <v>313</v>
+        <v>231</v>
       </c>
       <c r="Q62" t="s">
         <v>27</v>
       </c>
       <c r="R62" s="1">
-        <v>29527</v>
+        <v>33980</v>
       </c>
       <c r="S62" t="s">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="T62" t="s">
         <v>27</v>
@@ -10072,10 +10174,10 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="B63" t="s">
-        <v>316</v>
+        <v>234</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
@@ -10084,22 +10186,22 @@
         <v>23</v>
       </c>
       <c r="G63" s="1">
-        <v>45896</v>
+        <v>46055</v>
       </c>
       <c r="I63" t="s">
         <v>32</v>
       </c>
       <c r="J63" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="K63" t="s">
         <v>34</v>
       </c>
       <c r="L63">
-        <v>12179743627</v>
+        <v>12179044849</v>
       </c>
       <c r="M63">
-        <v>331088967</v>
+        <v>330075799</v>
       </c>
       <c r="N63" t="s">
         <v>27</v>
@@ -10108,16 +10210,16 @@
         <v>27</v>
       </c>
       <c r="P63" t="s">
-        <v>317</v>
+        <v>235</v>
       </c>
       <c r="Q63" t="s">
         <v>27</v>
       </c>
       <c r="R63" s="1">
-        <v>30955</v>
+        <v>27165</v>
       </c>
       <c r="S63" t="s">
-        <v>318</v>
+        <v>236</v>
       </c>
       <c r="T63" t="s">
         <v>27</v>
@@ -10125,10 +10227,10 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="B64" t="s">
-        <v>320</v>
+        <v>238</v>
       </c>
       <c r="C64" t="s">
         <v>22</v>
@@ -10137,22 +10239,22 @@
         <v>23</v>
       </c>
       <c r="G64" s="1">
-        <v>45985</v>
+        <v>45939</v>
       </c>
       <c r="I64" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J64" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="K64" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L64">
-        <v>12179364852</v>
+        <v>12179739349</v>
       </c>
       <c r="M64">
-        <v>334301521</v>
+        <v>331076535</v>
       </c>
       <c r="N64" t="s">
         <v>27</v>
@@ -10161,16 +10263,16 @@
         <v>27</v>
       </c>
       <c r="P64" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
       </c>
       <c r="R64" s="1">
-        <v>31315</v>
+        <v>33573</v>
       </c>
       <c r="S64" t="s">
-        <v>322</v>
+        <v>240</v>
       </c>
       <c r="T64" t="s">
         <v>27</v>
@@ -10178,10 +10280,10 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>323</v>
+        <v>241</v>
       </c>
       <c r="B65" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
       <c r="C65" t="s">
         <v>22</v>
@@ -10190,22 +10292,22 @@
         <v>23</v>
       </c>
       <c r="G65" s="1">
-        <v>46104</v>
+        <v>46070</v>
       </c>
       <c r="I65" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J65" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="K65" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L65">
-        <v>12183077022</v>
+        <v>12181747446</v>
       </c>
       <c r="M65">
-        <v>332680193</v>
+        <v>333014880</v>
       </c>
       <c r="N65" t="s">
         <v>27</v>
@@ -10214,16 +10316,16 @@
         <v>27</v>
       </c>
       <c r="P65" t="s">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="Q65" t="s">
         <v>27</v>
       </c>
       <c r="R65" s="1">
-        <v>33131</v>
+        <v>30064</v>
       </c>
       <c r="S65" t="s">
-        <v>326</v>
+        <v>244</v>
       </c>
       <c r="T65" t="s">
         <v>27</v>
@@ -10231,10 +10333,10 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>327</v>
+        <v>245</v>
       </c>
       <c r="B66" t="s">
-        <v>328</v>
+        <v>246</v>
       </c>
       <c r="C66" t="s">
         <v>22</v>
@@ -10243,22 +10345,22 @@
         <v>23</v>
       </c>
       <c r="G66" s="1">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="I66" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J66" t="s">
-        <v>268</v>
+        <v>33</v>
       </c>
       <c r="K66" t="s">
         <v>34</v>
       </c>
       <c r="L66">
-        <v>12175810810</v>
+        <v>12174925624</v>
       </c>
       <c r="M66">
-        <v>325621187</v>
+        <v>324698070</v>
       </c>
       <c r="N66" t="s">
         <v>27</v>
@@ -10267,16 +10369,16 @@
         <v>27</v>
       </c>
       <c r="P66" t="s">
-        <v>329</v>
+        <v>247</v>
       </c>
       <c r="Q66" t="s">
         <v>27</v>
       </c>
       <c r="R66" s="1">
-        <v>26505</v>
+        <v>31470</v>
       </c>
       <c r="S66" t="s">
-        <v>330</v>
+        <v>248</v>
       </c>
       <c r="T66" t="s">
         <v>27</v>
@@ -10284,10 +10386,10 @@
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>331</v>
+        <v>249</v>
       </c>
       <c r="B67" t="s">
-        <v>332</v>
+        <v>250</v>
       </c>
       <c r="C67" t="s">
         <v>22</v>
@@ -10296,22 +10398,22 @@
         <v>23</v>
       </c>
       <c r="G67" s="1">
-        <v>45939</v>
+        <v>46056</v>
       </c>
       <c r="I67" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J67" t="s">
-        <v>46</v>
+        <v>216</v>
       </c>
       <c r="K67" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="L67">
-        <v>12178120413</v>
+        <v>12179664378</v>
       </c>
       <c r="M67">
-        <v>328390950</v>
+        <v>331225549</v>
       </c>
       <c r="N67" t="s">
         <v>27</v>
@@ -10320,16 +10422,16 @@
         <v>27</v>
       </c>
       <c r="P67" t="s">
-        <v>333</v>
+        <v>251</v>
       </c>
       <c r="Q67" t="s">
         <v>27</v>
       </c>
       <c r="R67" s="1">
-        <v>33180</v>
+        <v>28805</v>
       </c>
       <c r="S67" t="s">
-        <v>334</v>
+        <v>252</v>
       </c>
       <c r="T67" t="s">
         <v>27</v>
@@ -10337,10 +10439,10 @@
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>335</v>
+        <v>253</v>
       </c>
       <c r="B68" t="s">
-        <v>336</v>
+        <v>254</v>
       </c>
       <c r="C68" t="s">
         <v>22</v>
@@ -10349,7 +10451,7 @@
         <v>23</v>
       </c>
       <c r="G68" s="1">
-        <v>45931</v>
+        <v>46042</v>
       </c>
       <c r="I68" t="s">
         <v>24</v>
@@ -10358,13 +10460,13 @@
         <v>255</v>
       </c>
       <c r="K68" t="s">
-        <v>337</v>
+        <v>41</v>
       </c>
       <c r="L68">
-        <v>12181577861</v>
+        <v>12179744347</v>
       </c>
       <c r="M68">
-        <v>331069245</v>
+        <v>331317052</v>
       </c>
       <c r="N68" t="s">
         <v>27</v>
@@ -10373,16 +10475,16 @@
         <v>27</v>
       </c>
       <c r="P68" t="s">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="Q68" t="s">
         <v>27</v>
       </c>
       <c r="R68" s="1">
-        <v>31297</v>
+        <v>29205</v>
       </c>
       <c r="S68" t="s">
-        <v>339</v>
+        <v>257</v>
       </c>
       <c r="T68" t="s">
         <v>27</v>
@@ -10390,10 +10492,10 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>340</v>
+        <v>258</v>
       </c>
       <c r="B69" t="s">
-        <v>341</v>
+        <v>259</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
@@ -10411,13 +10513,13 @@
         <v>109</v>
       </c>
       <c r="K69" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="L69">
-        <v>12179165027</v>
+        <v>12178112452</v>
       </c>
       <c r="M69">
-        <v>330253883</v>
+        <v>328342688</v>
       </c>
       <c r="N69" t="s">
         <v>27</v>
@@ -10426,16 +10528,16 @@
         <v>27</v>
       </c>
       <c r="P69" t="s">
-        <v>342</v>
+        <v>260</v>
       </c>
       <c r="Q69" t="s">
         <v>27</v>
       </c>
       <c r="R69" s="1">
-        <v>33588</v>
+        <v>32666</v>
       </c>
       <c r="S69" t="s">
-        <v>343</v>
+        <v>261</v>
       </c>
       <c r="T69" t="s">
         <v>27</v>
@@ -10443,10 +10545,10 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="B70" t="s">
-        <v>345</v>
+        <v>263</v>
       </c>
       <c r="C70" t="s">
         <v>22</v>
@@ -10455,22 +10557,22 @@
         <v>23</v>
       </c>
       <c r="G70" s="1">
-        <v>46055</v>
+        <v>46104</v>
       </c>
       <c r="I70" t="s">
         <v>32</v>
       </c>
       <c r="J70" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L70">
-        <v>12178400456</v>
+        <v>12079006901</v>
       </c>
       <c r="M70">
-        <v>328834220</v>
+        <v>299820505</v>
       </c>
       <c r="N70" t="s">
         <v>27</v>
@@ -10479,16 +10581,16 @@
         <v>27</v>
       </c>
       <c r="P70" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="Q70" t="s">
         <v>27</v>
       </c>
       <c r="R70" s="1">
-        <v>34324</v>
+        <v>35433</v>
       </c>
       <c r="S70" t="s">
-        <v>347</v>
+        <v>265</v>
       </c>
       <c r="T70" t="s">
         <v>27</v>
@@ -10496,10 +10598,10 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>348</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="C71" t="s">
         <v>22</v>
@@ -10508,22 +10610,22 @@
         <v>23</v>
       </c>
       <c r="G71" s="1">
-        <v>45957</v>
+        <v>46056</v>
       </c>
       <c r="I71" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J71" t="s">
-        <v>33</v>
+        <v>268</v>
       </c>
       <c r="K71" t="s">
         <v>34</v>
       </c>
       <c r="L71">
-        <v>12178120706</v>
+        <v>12178632699</v>
       </c>
       <c r="M71">
-        <v>328389900</v>
+        <v>329648357</v>
       </c>
       <c r="N71" t="s">
         <v>27</v>
@@ -10532,16 +10634,16 @@
         <v>27</v>
       </c>
       <c r="P71" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
       <c r="Q71" t="s">
         <v>27</v>
       </c>
       <c r="R71" s="1">
-        <v>28758</v>
+        <v>27183</v>
       </c>
       <c r="S71" t="s">
-        <v>351</v>
+        <v>270</v>
       </c>
       <c r="T71" t="s">
         <v>27</v>
@@ -10549,10 +10651,10 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="B72" t="s">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="C72" t="s">
         <v>22</v>
@@ -10561,22 +10663,22 @@
         <v>23</v>
       </c>
       <c r="G72" s="1">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="I72" t="s">
         <v>24</v>
       </c>
       <c r="J72" t="s">
-        <v>25</v>
+        <v>273</v>
       </c>
       <c r="K72" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L72">
-        <v>12177655172</v>
+        <v>12181598757</v>
       </c>
       <c r="M72">
-        <v>327778350</v>
+        <v>334281130</v>
       </c>
       <c r="N72" t="s">
         <v>27</v>
@@ -10585,16 +10687,16 @@
         <v>27</v>
       </c>
       <c r="P72" t="s">
-        <v>354</v>
+        <v>274</v>
       </c>
       <c r="Q72" t="s">
         <v>27</v>
       </c>
       <c r="R72" s="1">
-        <v>31317</v>
+        <v>28197</v>
       </c>
       <c r="S72" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="T72" t="s">
         <v>27</v>
@@ -10602,10 +10704,10 @@
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="B73" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="C73" t="s">
         <v>22</v>
@@ -10614,22 +10716,22 @@
         <v>23</v>
       </c>
       <c r="G73" s="1">
-        <v>46072</v>
+        <v>45939</v>
       </c>
       <c r="I73" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J73" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="K73" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L73">
-        <v>12182949611</v>
+        <v>12176828161</v>
       </c>
       <c r="M73">
-        <v>336117523</v>
+        <v>326856609</v>
       </c>
       <c r="N73" t="s">
         <v>27</v>
@@ -10638,16 +10740,16 @@
         <v>27</v>
       </c>
       <c r="P73" t="s">
-        <v>358</v>
+        <v>278</v>
       </c>
       <c r="Q73" t="s">
         <v>27</v>
       </c>
       <c r="R73" s="1">
-        <v>26767</v>
+        <v>31702</v>
       </c>
       <c r="S73" t="s">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="T73" t="s">
         <v>27</v>
@@ -10655,10 +10757,10 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="B74" t="s">
-        <v>361</v>
+        <v>281</v>
       </c>
       <c r="C74" t="s">
         <v>22</v>
@@ -10667,22 +10769,22 @@
         <v>23</v>
       </c>
       <c r="G74" s="1">
-        <v>46070</v>
+        <v>46055</v>
       </c>
       <c r="I74" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J74" t="s">
-        <v>119</v>
+        <v>282</v>
       </c>
       <c r="K74" t="s">
-        <v>47</v>
+        <v>283</v>
       </c>
       <c r="L74">
-        <v>12182361451</v>
+        <v>12181966542</v>
       </c>
       <c r="M74">
-        <v>332809730</v>
+        <v>334529387</v>
       </c>
       <c r="N74" t="s">
         <v>27</v>
@@ -10691,16 +10793,16 @@
         <v>27</v>
       </c>
       <c r="P74" t="s">
-        <v>362</v>
+        <v>284</v>
       </c>
       <c r="Q74" t="s">
         <v>27</v>
       </c>
       <c r="R74" s="1">
-        <v>32417</v>
+        <v>32610</v>
       </c>
       <c r="S74" t="s">
-        <v>363</v>
+        <v>285</v>
       </c>
       <c r="T74" t="s">
         <v>27</v>
@@ -10708,10 +10810,10 @@
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>364</v>
+        <v>286</v>
       </c>
       <c r="B75" t="s">
-        <v>365</v>
+        <v>287</v>
       </c>
       <c r="C75" t="s">
         <v>22</v>
@@ -10720,22 +10822,22 @@
         <v>23</v>
       </c>
       <c r="G75" s="1">
-        <v>46062</v>
+        <v>45931</v>
       </c>
       <c r="I75" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J75" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="K75" t="s">
-        <v>47</v>
+        <v>288</v>
       </c>
       <c r="L75">
-        <v>12177223999</v>
+        <v>12163300700</v>
       </c>
       <c r="M75">
-        <v>327217227</v>
+        <v>315756845</v>
       </c>
       <c r="N75" t="s">
         <v>27</v>
@@ -10744,16 +10846,16 @@
         <v>27</v>
       </c>
       <c r="P75" t="s">
-        <v>366</v>
+        <v>289</v>
       </c>
       <c r="Q75" t="s">
         <v>27</v>
       </c>
       <c r="R75" s="1">
-        <v>27389</v>
+        <v>29062</v>
       </c>
       <c r="S75" t="s">
-        <v>367</v>
+        <v>290</v>
       </c>
       <c r="T75" t="s">
         <v>27</v>
@@ -10761,10 +10863,10 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="B76" t="s">
-        <v>369</v>
+        <v>292</v>
       </c>
       <c r="C76" t="s">
         <v>22</v>
@@ -10773,22 +10875,22 @@
         <v>23</v>
       </c>
       <c r="G76" s="1">
-        <v>45922</v>
+        <v>46041</v>
       </c>
       <c r="I76" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J76" t="s">
-        <v>46</v>
+        <v>293</v>
       </c>
       <c r="K76" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L76">
-        <v>12179044831</v>
+        <v>12182503362</v>
       </c>
       <c r="M76">
-        <v>330173480</v>
+        <v>332775160</v>
       </c>
       <c r="N76" t="s">
         <v>27</v>
@@ -10797,16 +10899,16 @@
         <v>27</v>
       </c>
       <c r="P76" t="s">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="Q76" t="s">
         <v>27</v>
       </c>
       <c r="R76" s="1">
-        <v>30368</v>
+        <v>29192</v>
       </c>
       <c r="S76" t="s">
-        <v>371</v>
+        <v>295</v>
       </c>
       <c r="T76" t="s">
         <v>27</v>
@@ -10814,10 +10916,10 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>372</v>
+        <v>296</v>
       </c>
       <c r="B77" t="s">
-        <v>373</v>
+        <v>297</v>
       </c>
       <c r="C77" t="s">
         <v>22</v>
@@ -10826,22 +10928,22 @@
         <v>23</v>
       </c>
       <c r="G77" s="1">
-        <v>46072</v>
+        <v>45932</v>
       </c>
       <c r="I77" t="s">
         <v>24</v>
       </c>
       <c r="J77" t="s">
-        <v>374</v>
+        <v>298</v>
       </c>
       <c r="K77" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="L77">
-        <v>12182882910</v>
+        <v>12173783651</v>
       </c>
       <c r="M77">
-        <v>335903606</v>
+        <v>323430333</v>
       </c>
       <c r="N77" t="s">
         <v>27</v>
@@ -10850,16 +10952,16 @@
         <v>27</v>
       </c>
       <c r="P77" t="s">
-        <v>375</v>
+        <v>299</v>
       </c>
       <c r="Q77" t="s">
         <v>27</v>
       </c>
       <c r="R77" s="1">
-        <v>36248</v>
+        <v>25998</v>
       </c>
       <c r="S77" t="s">
-        <v>376</v>
+        <v>300</v>
       </c>
       <c r="T77" t="s">
         <v>27</v>
@@ -10867,10 +10969,10 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>377</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="C78" t="s">
         <v>22</v>
@@ -10879,22 +10981,22 @@
         <v>23</v>
       </c>
       <c r="G78" s="1">
-        <v>46055</v>
+        <v>46048</v>
       </c>
       <c r="I78" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J78" t="s">
-        <v>33</v>
+        <v>303</v>
       </c>
       <c r="K78" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L78">
-        <v>12177463795</v>
+        <v>12182792370</v>
       </c>
       <c r="M78">
-        <v>327466324</v>
+        <v>335824293</v>
       </c>
       <c r="N78" t="s">
         <v>27</v>
@@ -10903,16 +11005,16 @@
         <v>27</v>
       </c>
       <c r="P78" t="s">
-        <v>379</v>
+        <v>304</v>
       </c>
       <c r="Q78" t="s">
         <v>27</v>
       </c>
       <c r="R78" s="1">
-        <v>31203</v>
+        <v>31157</v>
       </c>
       <c r="S78" t="s">
-        <v>380</v>
+        <v>305</v>
       </c>
       <c r="T78" t="s">
         <v>27</v>
@@ -10920,10 +11022,10 @@
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>381</v>
+        <v>306</v>
       </c>
       <c r="B79" t="s">
-        <v>382</v>
+        <v>307</v>
       </c>
       <c r="C79" t="s">
         <v>22</v>
@@ -10932,22 +11034,22 @@
         <v>23</v>
       </c>
       <c r="G79" s="1">
-        <v>45926</v>
+        <v>46056</v>
       </c>
       <c r="I79" t="s">
         <v>24</v>
       </c>
       <c r="J79" t="s">
-        <v>86</v>
+        <v>268</v>
       </c>
       <c r="K79" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L79">
-        <v>12078814577</v>
+        <v>12178109682</v>
       </c>
       <c r="M79">
-        <v>299942767</v>
+        <v>328346098</v>
       </c>
       <c r="N79" t="s">
         <v>27</v>
@@ -10956,16 +11058,16 @@
         <v>27</v>
       </c>
       <c r="P79" t="s">
-        <v>383</v>
+        <v>308</v>
       </c>
       <c r="Q79" t="s">
         <v>27</v>
       </c>
       <c r="R79" s="1">
-        <v>34864</v>
+        <v>30162</v>
       </c>
       <c r="S79" t="s">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="T79" t="s">
         <v>27</v>
@@ -10973,10 +11075,10 @@
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>385</v>
+        <v>310</v>
       </c>
       <c r="B80" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="C80" t="s">
         <v>22</v>
@@ -10985,22 +11087,22 @@
         <v>23</v>
       </c>
       <c r="G80" s="1">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="I80" t="s">
         <v>24</v>
       </c>
       <c r="J80" t="s">
-        <v>387</v>
+        <v>312</v>
       </c>
       <c r="K80" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="L80">
-        <v>12179107493</v>
+        <v>12176592856</v>
       </c>
       <c r="M80">
-        <v>330317580</v>
+        <v>326550992</v>
       </c>
       <c r="N80" t="s">
         <v>27</v>
@@ -11009,16 +11111,16 @@
         <v>27</v>
       </c>
       <c r="P80" t="s">
-        <v>388</v>
+        <v>313</v>
       </c>
       <c r="Q80" t="s">
         <v>27</v>
       </c>
       <c r="R80" s="1">
-        <v>32943</v>
+        <v>29527</v>
       </c>
       <c r="S80" t="s">
-        <v>389</v>
+        <v>314</v>
       </c>
       <c r="T80" t="s">
         <v>27</v>
@@ -11026,10 +11128,10 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>390</v>
+        <v>315</v>
       </c>
       <c r="B81" t="s">
-        <v>391</v>
+        <v>316</v>
       </c>
       <c r="C81" t="s">
         <v>22</v>
@@ -11038,22 +11140,22 @@
         <v>23</v>
       </c>
       <c r="G81" s="1">
-        <v>46064</v>
+        <v>45896</v>
       </c>
       <c r="I81" t="s">
         <v>32</v>
       </c>
       <c r="J81" t="s">
-        <v>392</v>
+        <v>72</v>
       </c>
       <c r="K81" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L81">
-        <v>12181975613</v>
+        <v>12179743627</v>
       </c>
       <c r="M81">
-        <v>334064686</v>
+        <v>331088967</v>
       </c>
       <c r="N81" t="s">
         <v>27</v>
@@ -11062,16 +11164,16 @@
         <v>27</v>
       </c>
       <c r="P81" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="Q81" t="s">
         <v>27</v>
       </c>
       <c r="R81" s="1">
-        <v>28482</v>
+        <v>30955</v>
       </c>
       <c r="S81" t="s">
-        <v>394</v>
+        <v>318</v>
       </c>
       <c r="T81" t="s">
         <v>27</v>
@@ -11079,10 +11181,10 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>395</v>
+        <v>319</v>
       </c>
       <c r="B82" t="s">
-        <v>396</v>
+        <v>320</v>
       </c>
       <c r="C82" t="s">
         <v>22</v>
@@ -11091,22 +11193,22 @@
         <v>23</v>
       </c>
       <c r="G82" s="1">
-        <v>45939</v>
+        <v>45985</v>
       </c>
       <c r="I82" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J82" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="K82" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L82">
-        <v>12178313099</v>
+        <v>12179364852</v>
       </c>
       <c r="M82">
-        <v>329285807</v>
+        <v>334301521</v>
       </c>
       <c r="N82" t="s">
         <v>27</v>
@@ -11115,16 +11217,16 @@
         <v>27</v>
       </c>
       <c r="P82" t="s">
-        <v>397</v>
+        <v>321</v>
       </c>
       <c r="Q82" t="s">
         <v>27</v>
       </c>
       <c r="R82" s="1">
-        <v>28654</v>
+        <v>31315</v>
       </c>
       <c r="S82" t="s">
-        <v>398</v>
+        <v>322</v>
       </c>
       <c r="T82" t="s">
         <v>27</v>
@@ -11132,10 +11234,10 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>399</v>
+        <v>323</v>
       </c>
       <c r="B83" t="s">
-        <v>400</v>
+        <v>324</v>
       </c>
       <c r="C83" t="s">
         <v>22</v>
@@ -11144,22 +11246,22 @@
         <v>23</v>
       </c>
       <c r="G83" s="1">
-        <v>45945</v>
+        <v>46104</v>
       </c>
       <c r="I83" t="s">
         <v>32</v>
       </c>
       <c r="J83" t="s">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="K83" t="s">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="L83">
-        <v>12179250379</v>
+        <v>12183077022</v>
       </c>
       <c r="M83">
-        <v>330460560</v>
+        <v>332680193</v>
       </c>
       <c r="N83" t="s">
         <v>27</v>
@@ -11168,16 +11270,16 @@
         <v>27</v>
       </c>
       <c r="P83" t="s">
-        <v>402</v>
+        <v>325</v>
       </c>
       <c r="Q83" t="s">
         <v>27</v>
       </c>
       <c r="R83" s="1">
-        <v>30980</v>
+        <v>33131</v>
       </c>
       <c r="S83" t="s">
-        <v>403</v>
+        <v>326</v>
       </c>
       <c r="T83" t="s">
         <v>27</v>
@@ -11185,10 +11287,10 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>404</v>
+        <v>327</v>
       </c>
       <c r="B84" t="s">
-        <v>405</v>
+        <v>328</v>
       </c>
       <c r="C84" t="s">
         <v>22</v>
@@ -11197,22 +11299,22 @@
         <v>23</v>
       </c>
       <c r="G84" s="1">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="I84" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J84" t="s">
-        <v>129</v>
+        <v>268</v>
       </c>
       <c r="K84" t="s">
         <v>34</v>
       </c>
       <c r="L84">
-        <v>12174334636</v>
+        <v>12175810810</v>
       </c>
       <c r="M84">
-        <v>324013027</v>
+        <v>325621187</v>
       </c>
       <c r="N84" t="s">
         <v>27</v>
@@ -11221,16 +11323,16 @@
         <v>27</v>
       </c>
       <c r="P84" t="s">
-        <v>406</v>
+        <v>329</v>
       </c>
       <c r="Q84" t="s">
         <v>27</v>
       </c>
       <c r="R84" s="1">
-        <v>27058</v>
+        <v>26505</v>
       </c>
       <c r="S84" t="s">
-        <v>407</v>
+        <v>330</v>
       </c>
       <c r="T84" t="s">
         <v>27</v>
@@ -11238,10 +11340,10 @@
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>408</v>
+        <v>331</v>
       </c>
       <c r="B85" t="s">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="C85" t="s">
         <v>22</v>
@@ -11250,22 +11352,22 @@
         <v>23</v>
       </c>
       <c r="G85" s="1">
-        <v>46055</v>
+        <v>45939</v>
       </c>
       <c r="I85" t="s">
         <v>32</v>
       </c>
       <c r="J85" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K85" t="s">
         <v>47</v>
       </c>
       <c r="L85">
-        <v>12178024391</v>
+        <v>12178120413</v>
       </c>
       <c r="M85">
-        <v>328323586</v>
+        <v>328390950</v>
       </c>
       <c r="N85" t="s">
         <v>27</v>
@@ -11274,16 +11376,16 @@
         <v>27</v>
       </c>
       <c r="P85" t="s">
-        <v>410</v>
+        <v>333</v>
       </c>
       <c r="Q85" t="s">
         <v>27</v>
       </c>
       <c r="R85" s="1">
-        <v>29119</v>
+        <v>33180</v>
       </c>
       <c r="S85" t="s">
-        <v>411</v>
+        <v>334</v>
       </c>
       <c r="T85" t="s">
         <v>27</v>
@@ -11291,10 +11393,10 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>412</v>
+        <v>335</v>
       </c>
       <c r="B86" t="s">
-        <v>413</v>
+        <v>336</v>
       </c>
       <c r="C86" t="s">
         <v>22</v>
@@ -11312,13 +11414,13 @@
         <v>255</v>
       </c>
       <c r="K86" t="s">
-        <v>47</v>
+        <v>337</v>
       </c>
       <c r="L86">
-        <v>12168718380</v>
+        <v>12181577861</v>
       </c>
       <c r="M86">
-        <v>317389289</v>
+        <v>331069245</v>
       </c>
       <c r="N86" t="s">
         <v>27</v>
@@ -11327,16 +11429,16 @@
         <v>27</v>
       </c>
       <c r="P86" t="s">
-        <v>414</v>
+        <v>338</v>
       </c>
       <c r="Q86" t="s">
         <v>27</v>
       </c>
       <c r="R86" s="1">
-        <v>32564</v>
+        <v>31297</v>
       </c>
       <c r="S86" t="s">
-        <v>415</v>
+        <v>339</v>
       </c>
       <c r="T86" t="s">
         <v>27</v>
@@ -11344,10 +11446,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="B87" t="s">
-        <v>417</v>
+        <v>341</v>
       </c>
       <c r="C87" t="s">
         <v>22</v>
@@ -11356,22 +11458,22 @@
         <v>23</v>
       </c>
       <c r="G87" s="1">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="I87" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J87" t="s">
-        <v>418</v>
+        <v>109</v>
       </c>
       <c r="K87" t="s">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="L87">
-        <v>12179777155</v>
+        <v>12179165027</v>
       </c>
       <c r="M87">
-        <v>331299488</v>
+        <v>330253883</v>
       </c>
       <c r="N87" t="s">
         <v>27</v>
@@ -11380,16 +11482,16 @@
         <v>27</v>
       </c>
       <c r="P87" t="s">
-        <v>419</v>
+        <v>342</v>
       </c>
       <c r="Q87" t="s">
         <v>27</v>
       </c>
       <c r="R87" s="1">
-        <v>33460</v>
+        <v>33588</v>
       </c>
       <c r="S87" t="s">
-        <v>420</v>
+        <v>343</v>
       </c>
       <c r="T87" t="s">
         <v>27</v>
@@ -11397,10 +11499,10 @@
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>421</v>
+        <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>422</v>
+        <v>345</v>
       </c>
       <c r="C88" t="s">
         <v>22</v>
@@ -11415,16 +11517,16 @@
         <v>32</v>
       </c>
       <c r="J88" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="K88" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="L88">
-        <v>12177655203</v>
+        <v>12178400456</v>
       </c>
       <c r="M88">
-        <v>327777850</v>
+        <v>328834220</v>
       </c>
       <c r="N88" t="s">
         <v>27</v>
@@ -11433,16 +11535,16 @@
         <v>27</v>
       </c>
       <c r="P88" t="s">
-        <v>423</v>
+        <v>346</v>
       </c>
       <c r="Q88" t="s">
         <v>27</v>
       </c>
       <c r="R88" s="1">
-        <v>29007</v>
+        <v>34324</v>
       </c>
       <c r="S88" t="s">
-        <v>424</v>
+        <v>347</v>
       </c>
       <c r="T88" t="s">
         <v>27</v>
@@ -11450,10 +11552,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>425</v>
+        <v>348</v>
       </c>
       <c r="B89" t="s">
-        <v>426</v>
+        <v>349</v>
       </c>
       <c r="C89" t="s">
         <v>22</v>
@@ -11462,22 +11564,22 @@
         <v>23</v>
       </c>
       <c r="G89" s="1">
-        <v>46051</v>
+        <v>45957</v>
       </c>
       <c r="I89" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J89" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="K89" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L89">
-        <v>12181252685</v>
+        <v>12178120706</v>
       </c>
       <c r="M89">
-        <v>332699200</v>
+        <v>328389900</v>
       </c>
       <c r="N89" t="s">
         <v>27</v>
@@ -11486,16 +11588,16 @@
         <v>27</v>
       </c>
       <c r="P89" t="s">
-        <v>427</v>
+        <v>350</v>
       </c>
       <c r="Q89" t="s">
         <v>27</v>
       </c>
       <c r="R89" s="1">
-        <v>32333</v>
+        <v>28758</v>
       </c>
       <c r="S89" t="s">
-        <v>428</v>
+        <v>351</v>
       </c>
       <c r="T89" t="s">
         <v>27</v>
@@ -11503,10 +11605,10 @@
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>429</v>
+        <v>352</v>
       </c>
       <c r="B90" t="s">
-        <v>430</v>
+        <v>353</v>
       </c>
       <c r="C90" t="s">
         <v>22</v>
@@ -11515,22 +11617,22 @@
         <v>23</v>
       </c>
       <c r="G90" s="1">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="I90" t="s">
         <v>24</v>
       </c>
       <c r="J90" t="s">
-        <v>268</v>
+        <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L90">
-        <v>12178400414</v>
+        <v>12177655172</v>
       </c>
       <c r="M90">
-        <v>3299280015</v>
+        <v>327778350</v>
       </c>
       <c r="N90" t="s">
         <v>27</v>
@@ -11539,16 +11641,16 @@
         <v>27</v>
       </c>
       <c r="P90" t="s">
-        <v>431</v>
+        <v>354</v>
       </c>
       <c r="Q90" t="s">
         <v>27</v>
       </c>
       <c r="R90" s="1">
-        <v>25386</v>
+        <v>31317</v>
       </c>
       <c r="S90" t="s">
-        <v>432</v>
+        <v>355</v>
       </c>
       <c r="T90" t="s">
         <v>27</v>
@@ -11556,10 +11658,10 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>433</v>
+        <v>356</v>
       </c>
       <c r="B91" t="s">
-        <v>434</v>
+        <v>357</v>
       </c>
       <c r="C91" t="s">
         <v>22</v>
@@ -11568,22 +11670,22 @@
         <v>23</v>
       </c>
       <c r="G91" s="1">
-        <v>46055</v>
+        <v>46072</v>
       </c>
       <c r="I91" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J91" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K91" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L91">
-        <v>12177878414</v>
+        <v>12182949611</v>
       </c>
       <c r="M91">
-        <v>328009865</v>
+        <v>336117523</v>
       </c>
       <c r="N91" t="s">
         <v>27</v>
@@ -11592,16 +11694,16 @@
         <v>27</v>
       </c>
       <c r="P91" t="s">
-        <v>435</v>
+        <v>358</v>
       </c>
       <c r="Q91" t="s">
         <v>27</v>
       </c>
       <c r="R91" s="1">
-        <v>31754</v>
+        <v>26767</v>
       </c>
       <c r="S91" t="s">
-        <v>436</v>
+        <v>359</v>
       </c>
       <c r="T91" t="s">
         <v>27</v>
@@ -11609,10 +11711,10 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>437</v>
+        <v>360</v>
       </c>
       <c r="B92" t="s">
-        <v>438</v>
+        <v>361</v>
       </c>
       <c r="C92" t="s">
         <v>22</v>
@@ -11633,10 +11735,10 @@
         <v>47</v>
       </c>
       <c r="L92">
-        <v>12178172662</v>
+        <v>12182361451</v>
       </c>
       <c r="M92">
-        <v>328844705</v>
+        <v>332809730</v>
       </c>
       <c r="N92" t="s">
         <v>27</v>
@@ -11645,16 +11747,16 @@
         <v>27</v>
       </c>
       <c r="P92" t="s">
-        <v>439</v>
+        <v>362</v>
       </c>
       <c r="Q92" t="s">
         <v>27</v>
       </c>
       <c r="R92" s="1">
-        <v>32933</v>
+        <v>32417</v>
       </c>
       <c r="S92" t="s">
-        <v>440</v>
+        <v>363</v>
       </c>
       <c r="T92" t="s">
         <v>27</v>
@@ -11662,10 +11764,10 @@
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>441</v>
+        <v>364</v>
       </c>
       <c r="B93" t="s">
-        <v>442</v>
+        <v>365</v>
       </c>
       <c r="C93" t="s">
         <v>22</v>
@@ -11674,22 +11776,22 @@
         <v>23</v>
       </c>
       <c r="G93" s="1">
-        <v>46013</v>
+        <v>46062</v>
       </c>
       <c r="I93" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J93" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="K93" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L93">
-        <v>12180238056</v>
+        <v>12177223999</v>
       </c>
       <c r="M93">
-        <v>331861380</v>
+        <v>327217227</v>
       </c>
       <c r="N93" t="s">
         <v>27</v>
@@ -11698,16 +11800,16 @@
         <v>27</v>
       </c>
       <c r="P93" t="s">
-        <v>443</v>
+        <v>366</v>
       </c>
       <c r="Q93" t="s">
         <v>27</v>
       </c>
       <c r="R93" s="1">
-        <v>34267</v>
+        <v>27389</v>
       </c>
       <c r="S93" t="s">
-        <v>444</v>
+        <v>367</v>
       </c>
       <c r="T93" t="s">
         <v>27</v>
@@ -11715,10 +11817,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>445</v>
+        <v>368</v>
       </c>
       <c r="B94" t="s">
-        <v>446</v>
+        <v>369</v>
       </c>
       <c r="C94" t="s">
         <v>22</v>
@@ -11727,22 +11829,22 @@
         <v>23</v>
       </c>
       <c r="G94" s="1">
-        <v>46052</v>
+        <v>45922</v>
       </c>
       <c r="I94" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J94" t="s">
-        <v>273</v>
+        <v>46</v>
       </c>
       <c r="K94" t="s">
         <v>34</v>
       </c>
       <c r="L94">
-        <v>12179073005</v>
+        <v>12179044831</v>
       </c>
       <c r="M94">
-        <v>330304704</v>
+        <v>330173480</v>
       </c>
       <c r="N94" t="s">
         <v>27</v>
@@ -11751,16 +11853,16 @@
         <v>27</v>
       </c>
       <c r="P94" t="s">
-        <v>447</v>
+        <v>370</v>
       </c>
       <c r="Q94" t="s">
         <v>27</v>
       </c>
       <c r="R94" s="1">
-        <v>30929</v>
+        <v>30368</v>
       </c>
       <c r="S94" t="s">
-        <v>448</v>
+        <v>371</v>
       </c>
       <c r="T94" t="s">
         <v>27</v>
@@ -11768,10 +11870,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>449</v>
+        <v>372</v>
       </c>
       <c r="B95" t="s">
-        <v>450</v>
+        <v>373</v>
       </c>
       <c r="C95" t="s">
         <v>22</v>
@@ -11780,22 +11882,22 @@
         <v>23</v>
       </c>
       <c r="G95" s="1">
-        <v>46115</v>
+        <v>46072</v>
       </c>
       <c r="I95" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J95" t="s">
-        <v>203</v>
+        <v>374</v>
       </c>
       <c r="K95" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="L95">
-        <v>12183573996</v>
+        <v>12182882910</v>
       </c>
       <c r="M95">
-        <v>335618480</v>
+        <v>335903606</v>
       </c>
       <c r="N95" t="s">
         <v>27</v>
@@ -11804,16 +11906,16 @@
         <v>27</v>
       </c>
       <c r="P95" t="s">
-        <v>451</v>
+        <v>375</v>
       </c>
       <c r="Q95" t="s">
         <v>27</v>
       </c>
       <c r="R95" s="1">
-        <v>34887</v>
+        <v>36248</v>
       </c>
       <c r="S95" t="s">
-        <v>452</v>
+        <v>376</v>
       </c>
       <c r="T95" t="s">
         <v>27</v>
@@ -11821,10 +11923,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>453</v>
+        <v>377</v>
       </c>
       <c r="B96" t="s">
-        <v>454</v>
+        <v>378</v>
       </c>
       <c r="C96" t="s">
         <v>22</v>
@@ -11833,7 +11935,7 @@
         <v>23</v>
       </c>
       <c r="G96" s="1">
-        <v>45945</v>
+        <v>46055</v>
       </c>
       <c r="I96" t="s">
         <v>32</v>
@@ -11845,10 +11947,10 @@
         <v>34</v>
       </c>
       <c r="L96">
-        <v>12174814740</v>
+        <v>12177463795</v>
       </c>
       <c r="M96">
-        <v>324582960</v>
+        <v>327466324</v>
       </c>
       <c r="N96" t="s">
         <v>27</v>
@@ -11857,16 +11959,16 @@
         <v>27</v>
       </c>
       <c r="P96" t="s">
-        <v>455</v>
+        <v>379</v>
       </c>
       <c r="Q96" t="s">
         <v>27</v>
       </c>
       <c r="R96" s="1">
-        <v>28360</v>
+        <v>31203</v>
       </c>
       <c r="S96" t="s">
-        <v>456</v>
+        <v>380</v>
       </c>
       <c r="T96" t="s">
         <v>27</v>
@@ -11874,10 +11976,10 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>457</v>
+        <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>458</v>
+        <v>382</v>
       </c>
       <c r="C97" t="s">
         <v>22</v>
@@ -11886,22 +11988,22 @@
         <v>23</v>
       </c>
       <c r="G97" s="1">
-        <v>46052</v>
+        <v>45926</v>
       </c>
       <c r="I97" t="s">
         <v>24</v>
       </c>
       <c r="J97" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="K97" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L97">
-        <v>12182556875</v>
+        <v>12078814577</v>
       </c>
       <c r="M97">
-        <v>335261400</v>
+        <v>299942767</v>
       </c>
       <c r="N97" t="s">
         <v>27</v>
@@ -11910,16 +12012,16 @@
         <v>27</v>
       </c>
       <c r="P97" t="s">
-        <v>459</v>
+        <v>383</v>
       </c>
       <c r="Q97" t="s">
         <v>27</v>
       </c>
       <c r="R97" s="1">
-        <v>31537</v>
+        <v>34864</v>
       </c>
       <c r="S97" t="s">
-        <v>460</v>
+        <v>384</v>
       </c>
       <c r="T97" t="s">
         <v>27</v>
@@ -11927,10 +12029,10 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>461</v>
+        <v>385</v>
       </c>
       <c r="B98" t="s">
-        <v>462</v>
+        <v>386</v>
       </c>
       <c r="C98" t="s">
         <v>22</v>
@@ -11939,22 +12041,22 @@
         <v>23</v>
       </c>
       <c r="G98" s="1">
-        <v>46010</v>
+        <v>46056</v>
       </c>
       <c r="I98" t="s">
         <v>24</v>
       </c>
       <c r="J98" t="s">
-        <v>198</v>
+        <v>387</v>
       </c>
       <c r="K98" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="L98">
-        <v>12179711076</v>
+        <v>12179107493</v>
       </c>
       <c r="M98">
-        <v>331238543</v>
+        <v>330317580</v>
       </c>
       <c r="N98" t="s">
         <v>27</v>
@@ -11963,16 +12065,16 @@
         <v>27</v>
       </c>
       <c r="P98" t="s">
-        <v>463</v>
+        <v>388</v>
       </c>
       <c r="Q98" t="s">
         <v>27</v>
       </c>
       <c r="R98" s="1">
-        <v>31766</v>
+        <v>32943</v>
       </c>
       <c r="S98" t="s">
-        <v>464</v>
+        <v>389</v>
       </c>
       <c r="T98" t="s">
         <v>27</v>
@@ -11980,10 +12082,10 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>465</v>
+        <v>390</v>
       </c>
       <c r="B99" t="s">
-        <v>466</v>
+        <v>391</v>
       </c>
       <c r="C99" t="s">
         <v>22</v>
@@ -11992,22 +12094,22 @@
         <v>23</v>
       </c>
       <c r="G99" s="1">
-        <v>45902</v>
+        <v>46064</v>
       </c>
       <c r="I99" t="s">
         <v>32</v>
       </c>
       <c r="J99" t="s">
-        <v>33</v>
+        <v>392</v>
       </c>
       <c r="K99" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L99">
-        <v>12167306156</v>
+        <v>12181975613</v>
       </c>
       <c r="M99">
-        <v>317358855</v>
+        <v>334064686</v>
       </c>
       <c r="N99" t="s">
         <v>27</v>
@@ -12016,16 +12118,16 @@
         <v>27</v>
       </c>
       <c r="P99" t="s">
-        <v>467</v>
+        <v>393</v>
       </c>
       <c r="Q99" t="s">
         <v>27</v>
       </c>
       <c r="R99" s="1">
-        <v>34437</v>
+        <v>28482</v>
       </c>
       <c r="S99" t="s">
-        <v>468</v>
+        <v>394</v>
       </c>
       <c r="T99" t="s">
         <v>27</v>
@@ -12033,10 +12135,10 @@
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>469</v>
+        <v>395</v>
       </c>
       <c r="B100" t="s">
-        <v>470</v>
+        <v>396</v>
       </c>
       <c r="C100" t="s">
         <v>22</v>
@@ -12045,22 +12147,22 @@
         <v>23</v>
       </c>
       <c r="G100" s="1">
-        <v>46063</v>
+        <v>45939</v>
       </c>
       <c r="I100" t="s">
         <v>32</v>
       </c>
       <c r="J100" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="K100" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="L100">
-        <v>12182917078</v>
+        <v>12178313099</v>
       </c>
       <c r="M100">
-        <v>335769594</v>
+        <v>329285807</v>
       </c>
       <c r="N100" t="s">
         <v>27</v>
@@ -12069,16 +12171,16 @@
         <v>27</v>
       </c>
       <c r="P100" t="s">
-        <v>471</v>
+        <v>397</v>
       </c>
       <c r="Q100" t="s">
         <v>27</v>
       </c>
       <c r="R100" s="1">
-        <v>31756</v>
+        <v>28654</v>
       </c>
       <c r="S100" t="s">
-        <v>472</v>
+        <v>398</v>
       </c>
       <c r="T100" t="s">
         <v>27</v>
@@ -12086,10 +12188,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>473</v>
+        <v>399</v>
       </c>
       <c r="B101" t="s">
-        <v>474</v>
+        <v>400</v>
       </c>
       <c r="C101" t="s">
         <v>22</v>
@@ -12098,22 +12200,22 @@
         <v>23</v>
       </c>
       <c r="G101" s="1">
-        <v>46055</v>
+        <v>45945</v>
       </c>
       <c r="I101" t="s">
         <v>32</v>
       </c>
       <c r="J101" t="s">
-        <v>33</v>
+        <v>401</v>
       </c>
       <c r="K101" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="L101">
-        <v>12175238375</v>
+        <v>12179250379</v>
       </c>
       <c r="M101">
-        <v>325064172</v>
+        <v>330460560</v>
       </c>
       <c r="N101" t="s">
         <v>27</v>
@@ -12122,16 +12224,16 @@
         <v>27</v>
       </c>
       <c r="P101" t="s">
-        <v>475</v>
+        <v>402</v>
       </c>
       <c r="Q101" t="s">
         <v>27</v>
       </c>
       <c r="R101" s="1">
-        <v>34435</v>
+        <v>30980</v>
       </c>
       <c r="S101" t="s">
-        <v>476</v>
+        <v>403</v>
       </c>
       <c r="T101" t="s">
         <v>27</v>
@@ -12139,10 +12241,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>477</v>
+        <v>404</v>
       </c>
       <c r="B102" t="s">
-        <v>478</v>
+        <v>405</v>
       </c>
       <c r="C102" t="s">
         <v>22</v>
@@ -12151,22 +12253,22 @@
         <v>23</v>
       </c>
       <c r="G102" s="1">
-        <v>46104</v>
+        <v>46055</v>
       </c>
       <c r="I102" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J102" t="s">
-        <v>479</v>
+        <v>129</v>
       </c>
       <c r="K102" t="s">
         <v>34</v>
       </c>
       <c r="L102">
-        <v>12183153716</v>
+        <v>12174334636</v>
       </c>
       <c r="M102">
-        <v>333148940</v>
+        <v>324013027</v>
       </c>
       <c r="N102" t="s">
         <v>27</v>
@@ -12175,16 +12277,16 @@
         <v>27</v>
       </c>
       <c r="P102" t="s">
-        <v>480</v>
+        <v>406</v>
       </c>
       <c r="Q102" t="s">
         <v>27</v>
       </c>
       <c r="R102" s="1">
-        <v>31149</v>
+        <v>27058</v>
       </c>
       <c r="S102" t="s">
-        <v>481</v>
+        <v>407</v>
       </c>
       <c r="T102" t="s">
         <v>27</v>
@@ -12192,10 +12294,10 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>482</v>
+        <v>408</v>
       </c>
       <c r="B103" t="s">
-        <v>483</v>
+        <v>409</v>
       </c>
       <c r="C103" t="s">
         <v>22</v>
@@ -12204,22 +12306,22 @@
         <v>23</v>
       </c>
       <c r="G103" s="1">
-        <v>45887</v>
+        <v>46055</v>
       </c>
       <c r="I103" t="s">
         <v>32</v>
       </c>
       <c r="J103" t="s">
-        <v>484</v>
+        <v>33</v>
       </c>
       <c r="K103" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="L103">
-        <v>12175808914</v>
+        <v>12178024391</v>
       </c>
       <c r="M103">
-        <v>325618283</v>
+        <v>328323586</v>
       </c>
       <c r="N103" t="s">
         <v>27</v>
@@ -12228,16 +12330,16 @@
         <v>27</v>
       </c>
       <c r="P103" t="s">
-        <v>485</v>
+        <v>410</v>
       </c>
       <c r="Q103" t="s">
         <v>27</v>
       </c>
       <c r="R103" s="1">
-        <v>31428</v>
+        <v>29119</v>
       </c>
       <c r="S103" t="s">
-        <v>486</v>
+        <v>411</v>
       </c>
       <c r="T103" t="s">
         <v>27</v>
@@ -12245,10 +12347,10 @@
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>487</v>
+        <v>412</v>
       </c>
       <c r="B104" t="s">
-        <v>488</v>
+        <v>413</v>
       </c>
       <c r="C104" t="s">
         <v>22</v>
@@ -12257,22 +12359,22 @@
         <v>23</v>
       </c>
       <c r="G104" s="1">
-        <v>46028</v>
+        <v>45931</v>
       </c>
       <c r="I104" t="s">
         <v>24</v>
       </c>
       <c r="J104" t="s">
-        <v>135</v>
+        <v>255</v>
       </c>
       <c r="K104" t="s">
         <v>47</v>
       </c>
       <c r="L104">
-        <v>12177579535</v>
+        <v>12168718380</v>
       </c>
       <c r="M104">
-        <v>327803886</v>
+        <v>317389289</v>
       </c>
       <c r="N104" t="s">
         <v>27</v>
@@ -12281,16 +12383,16 @@
         <v>27</v>
       </c>
       <c r="P104" t="s">
-        <v>489</v>
+        <v>414</v>
       </c>
       <c r="Q104" t="s">
         <v>27</v>
       </c>
       <c r="R104" s="1">
-        <v>32239</v>
+        <v>32564</v>
       </c>
       <c r="S104" t="s">
-        <v>490</v>
+        <v>415</v>
       </c>
       <c r="T104" t="s">
         <v>27</v>
@@ -12298,10 +12400,10 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>491</v>
+        <v>416</v>
       </c>
       <c r="B105" t="s">
-        <v>492</v>
+        <v>417</v>
       </c>
       <c r="C105" t="s">
         <v>22</v>
@@ -12310,22 +12412,22 @@
         <v>23</v>
       </c>
       <c r="G105" s="1">
-        <v>46066</v>
+        <v>46076</v>
       </c>
       <c r="I105" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J105" t="s">
-        <v>203</v>
+        <v>418</v>
       </c>
       <c r="K105" t="s">
-        <v>41</v>
+        <v>283</v>
       </c>
       <c r="L105">
-        <v>12178131437</v>
+        <v>12179777155</v>
       </c>
       <c r="M105">
-        <v>328297852</v>
+        <v>331299488</v>
       </c>
       <c r="N105" t="s">
         <v>27</v>
@@ -12334,16 +12436,16 @@
         <v>27</v>
       </c>
       <c r="P105" t="s">
-        <v>493</v>
+        <v>419</v>
       </c>
       <c r="Q105" t="s">
         <v>27</v>
       </c>
       <c r="R105" s="1">
-        <v>31004</v>
+        <v>33460</v>
       </c>
       <c r="S105" t="s">
-        <v>494</v>
+        <v>420</v>
       </c>
       <c r="T105" t="s">
         <v>27</v>
@@ -12351,10 +12453,10 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>495</v>
+        <v>421</v>
       </c>
       <c r="B106" t="s">
-        <v>496</v>
+        <v>422</v>
       </c>
       <c r="C106" t="s">
         <v>22</v>
@@ -12372,13 +12474,13 @@
         <v>109</v>
       </c>
       <c r="K106" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="L106">
-        <v>12176382716</v>
+        <v>12177655203</v>
       </c>
       <c r="M106">
-        <v>326243879</v>
+        <v>327777850</v>
       </c>
       <c r="N106" t="s">
         <v>27</v>
@@ -12387,16 +12489,16 @@
         <v>27</v>
       </c>
       <c r="P106" t="s">
-        <v>497</v>
+        <v>423</v>
       </c>
       <c r="Q106" t="s">
         <v>27</v>
       </c>
       <c r="R106" s="1">
-        <v>30353</v>
+        <v>29007</v>
       </c>
       <c r="S106" t="s">
-        <v>498</v>
+        <v>424</v>
       </c>
       <c r="T106" t="s">
         <v>27</v>
@@ -12404,10 +12506,10 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>499</v>
+        <v>425</v>
       </c>
       <c r="B107" t="s">
-        <v>500</v>
+        <v>426</v>
       </c>
       <c r="C107" t="s">
         <v>22</v>
@@ -12416,22 +12518,22 @@
         <v>23</v>
       </c>
       <c r="G107" s="1">
-        <v>45926</v>
+        <v>46051</v>
       </c>
       <c r="I107" t="s">
         <v>24</v>
       </c>
       <c r="J107" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K107" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L107">
-        <v>12088460498</v>
+        <v>12181252685</v>
       </c>
       <c r="M107">
-        <v>308483820</v>
+        <v>332699200</v>
       </c>
       <c r="N107" t="s">
         <v>27</v>
@@ -12440,16 +12542,16 @@
         <v>27</v>
       </c>
       <c r="P107" t="s">
-        <v>501</v>
+        <v>427</v>
       </c>
       <c r="Q107" t="s">
         <v>27</v>
       </c>
       <c r="R107" s="1">
-        <v>27288</v>
+        <v>32333</v>
       </c>
       <c r="S107" t="s">
-        <v>502</v>
+        <v>428</v>
       </c>
       <c r="T107" t="s">
         <v>27</v>
@@ -12457,10 +12559,10 @@
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>503</v>
+        <v>429</v>
       </c>
       <c r="B108" t="s">
-        <v>504</v>
+        <v>430</v>
       </c>
       <c r="C108" t="s">
         <v>22</v>
@@ -12469,22 +12571,22 @@
         <v>23</v>
       </c>
       <c r="G108" s="1">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="I108" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J108" t="s">
-        <v>33</v>
+        <v>268</v>
       </c>
       <c r="K108" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L108">
-        <v>12176031515</v>
+        <v>12178400414</v>
       </c>
       <c r="M108">
-        <v>325892270</v>
+        <v>3299280015</v>
       </c>
       <c r="N108" t="s">
         <v>27</v>
@@ -12493,16 +12595,16 @@
         <v>27</v>
       </c>
       <c r="P108" t="s">
-        <v>505</v>
+        <v>431</v>
       </c>
       <c r="Q108" t="s">
         <v>27</v>
       </c>
       <c r="R108" s="1">
-        <v>27347</v>
+        <v>25386</v>
       </c>
       <c r="S108" t="s">
-        <v>506</v>
+        <v>432</v>
       </c>
       <c r="T108" t="s">
         <v>27</v>
@@ -12510,10 +12612,10 @@
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>507</v>
+        <v>433</v>
       </c>
       <c r="B109" t="s">
-        <v>508</v>
+        <v>434</v>
       </c>
       <c r="C109" t="s">
         <v>22</v>
@@ -12522,22 +12624,22 @@
         <v>23</v>
       </c>
       <c r="G109" s="1">
-        <v>46065</v>
+        <v>46055</v>
       </c>
       <c r="I109" t="s">
         <v>32</v>
       </c>
       <c r="J109" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="K109" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L109">
-        <v>12178337176</v>
+        <v>12177878414</v>
       </c>
       <c r="M109">
-        <v>329281011</v>
+        <v>328009865</v>
       </c>
       <c r="N109" t="s">
         <v>27</v>
@@ -12546,16 +12648,16 @@
         <v>27</v>
       </c>
       <c r="P109" t="s">
-        <v>509</v>
+        <v>435</v>
       </c>
       <c r="Q109" t="s">
         <v>27</v>
       </c>
       <c r="R109" s="1">
-        <v>24624</v>
+        <v>31754</v>
       </c>
       <c r="S109" t="s">
-        <v>510</v>
+        <v>436</v>
       </c>
       <c r="T109" t="s">
         <v>27</v>
@@ -12563,10 +12665,10 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>511</v>
+        <v>437</v>
       </c>
       <c r="B110" t="s">
-        <v>512</v>
+        <v>438</v>
       </c>
       <c r="C110" t="s">
         <v>22</v>
@@ -12575,22 +12677,22 @@
         <v>23</v>
       </c>
       <c r="G110" s="1">
-        <v>45931</v>
+        <v>46070</v>
       </c>
       <c r="I110" t="s">
         <v>24</v>
       </c>
       <c r="J110" t="s">
-        <v>255</v>
+        <v>119</v>
       </c>
       <c r="K110" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="L110">
-        <v>12091179354</v>
+        <v>12178172662</v>
       </c>
       <c r="M110">
-        <v>311567088</v>
+        <v>328844705</v>
       </c>
       <c r="N110" t="s">
         <v>27</v>
@@ -12599,16 +12701,16 @@
         <v>27</v>
       </c>
       <c r="P110" t="s">
-        <v>513</v>
+        <v>439</v>
       </c>
       <c r="Q110" t="s">
         <v>27</v>
       </c>
       <c r="R110" s="1">
-        <v>28379</v>
+        <v>32933</v>
       </c>
       <c r="S110" t="s">
-        <v>514</v>
+        <v>440</v>
       </c>
       <c r="T110" t="s">
         <v>27</v>
@@ -12616,10 +12718,10 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>515</v>
+        <v>441</v>
       </c>
       <c r="B111" t="s">
-        <v>516</v>
+        <v>442</v>
       </c>
       <c r="C111" t="s">
         <v>22</v>
@@ -12628,22 +12730,22 @@
         <v>23</v>
       </c>
       <c r="G111" s="1">
-        <v>46055</v>
+        <v>46013</v>
       </c>
       <c r="I111" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J111" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="K111" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="L111">
-        <v>12180291059</v>
+        <v>12180238056</v>
       </c>
       <c r="M111">
-        <v>331124432</v>
+        <v>331861380</v>
       </c>
       <c r="N111" t="s">
         <v>27</v>
@@ -12652,16 +12754,16 @@
         <v>27</v>
       </c>
       <c r="P111" t="s">
-        <v>517</v>
+        <v>443</v>
       </c>
       <c r="Q111" t="s">
         <v>27</v>
       </c>
       <c r="R111" s="1">
-        <v>27529</v>
+        <v>34267</v>
       </c>
       <c r="S111" t="s">
-        <v>518</v>
+        <v>444</v>
       </c>
       <c r="T111" t="s">
         <v>27</v>
@@ -12669,10 +12771,10 @@
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>519</v>
+        <v>445</v>
       </c>
       <c r="B112" t="s">
-        <v>520</v>
+        <v>446</v>
       </c>
       <c r="C112" t="s">
         <v>22</v>
@@ -12681,22 +12783,22 @@
         <v>23</v>
       </c>
       <c r="G112" s="1">
-        <v>45939</v>
+        <v>46052</v>
       </c>
       <c r="I112" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J112" t="s">
-        <v>46</v>
+        <v>273</v>
       </c>
       <c r="K112" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L112">
-        <v>12178130775</v>
+        <v>12179073005</v>
       </c>
       <c r="M112">
-        <v>328405256</v>
+        <v>330304704</v>
       </c>
       <c r="N112" t="s">
         <v>27</v>
@@ -12705,16 +12807,16 @@
         <v>27</v>
       </c>
       <c r="P112" t="s">
-        <v>521</v>
+        <v>447</v>
       </c>
       <c r="Q112" t="s">
         <v>27</v>
       </c>
       <c r="R112" s="1">
-        <v>29133</v>
+        <v>30929</v>
       </c>
       <c r="S112" t="s">
-        <v>522</v>
+        <v>448</v>
       </c>
       <c r="T112" t="s">
         <v>27</v>
@@ -12722,10 +12824,10 @@
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>523</v>
+        <v>449</v>
       </c>
       <c r="B113" t="s">
-        <v>524</v>
+        <v>450</v>
       </c>
       <c r="C113" t="s">
         <v>22</v>
@@ -12734,22 +12836,22 @@
         <v>23</v>
       </c>
       <c r="G113" s="1">
-        <v>45980</v>
+        <v>46115</v>
       </c>
       <c r="I113" t="s">
         <v>32</v>
       </c>
       <c r="J113" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="K113" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L113">
-        <v>12181939360</v>
+        <v>12183573996</v>
       </c>
       <c r="M113">
-        <v>334654149</v>
+        <v>335618480</v>
       </c>
       <c r="N113" t="s">
         <v>27</v>
@@ -12758,16 +12860,16 @@
         <v>27</v>
       </c>
       <c r="P113" t="s">
-        <v>525</v>
+        <v>451</v>
       </c>
       <c r="Q113" t="s">
         <v>27</v>
       </c>
       <c r="R113" s="1">
-        <v>28075</v>
+        <v>34887</v>
       </c>
       <c r="S113" t="s">
-        <v>526</v>
+        <v>452</v>
       </c>
       <c r="T113" t="s">
         <v>27</v>
@@ -12775,10 +12877,10 @@
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>527</v>
+        <v>453</v>
       </c>
       <c r="B114" t="s">
-        <v>528</v>
+        <v>454</v>
       </c>
       <c r="C114" t="s">
         <v>22</v>
@@ -12787,22 +12889,22 @@
         <v>23</v>
       </c>
       <c r="G114" s="1">
-        <v>46065</v>
+        <v>45945</v>
       </c>
       <c r="I114" t="s">
         <v>32</v>
       </c>
       <c r="J114" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="K114" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L114">
-        <v>12181910725</v>
+        <v>12174814740</v>
       </c>
       <c r="M114">
-        <v>331773473</v>
+        <v>324582960</v>
       </c>
       <c r="N114" t="s">
         <v>27</v>
@@ -12811,16 +12913,16 @@
         <v>27</v>
       </c>
       <c r="P114" t="s">
-        <v>529</v>
+        <v>455</v>
       </c>
       <c r="Q114" t="s">
         <v>27</v>
       </c>
       <c r="R114" s="1">
-        <v>28183</v>
+        <v>28360</v>
       </c>
       <c r="S114" t="s">
-        <v>530</v>
+        <v>456</v>
       </c>
       <c r="T114" t="s">
         <v>27</v>
@@ -12828,10 +12930,10 @@
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>531</v>
+        <v>457</v>
       </c>
       <c r="B115" t="s">
-        <v>532</v>
+        <v>458</v>
       </c>
       <c r="C115" t="s">
         <v>22</v>
@@ -12840,22 +12942,22 @@
         <v>23</v>
       </c>
       <c r="G115" s="1">
-        <v>46055</v>
+        <v>46052</v>
       </c>
       <c r="I115" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J115" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="K115" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L115">
-        <v>12174324251</v>
+        <v>12182556875</v>
       </c>
       <c r="M115">
-        <v>324044895</v>
+        <v>335261400</v>
       </c>
       <c r="N115" t="s">
         <v>27</v>
@@ -12864,16 +12966,16 @@
         <v>27</v>
       </c>
       <c r="P115" t="s">
-        <v>533</v>
+        <v>459</v>
       </c>
       <c r="Q115" t="s">
         <v>27</v>
       </c>
       <c r="R115" s="1">
-        <v>30735</v>
+        <v>31537</v>
       </c>
       <c r="S115" t="s">
-        <v>534</v>
+        <v>460</v>
       </c>
       <c r="T115" t="s">
         <v>27</v>
@@ -12881,10 +12983,10 @@
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>535</v>
+        <v>461</v>
       </c>
       <c r="B116" t="s">
-        <v>536</v>
+        <v>462</v>
       </c>
       <c r="C116" t="s">
         <v>22</v>
@@ -12893,22 +12995,22 @@
         <v>23</v>
       </c>
       <c r="G116" s="1">
-        <v>46072</v>
+        <v>46010</v>
       </c>
       <c r="I116" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J116" t="s">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="K116" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="L116">
-        <v>12177618206</v>
+        <v>12179711076</v>
       </c>
       <c r="M116">
-        <v>328046370</v>
+        <v>331238543</v>
       </c>
       <c r="N116" t="s">
         <v>27</v>
@@ -12917,16 +13019,16 @@
         <v>27</v>
       </c>
       <c r="P116" t="s">
-        <v>537</v>
+        <v>463</v>
       </c>
       <c r="Q116" t="s">
         <v>27</v>
       </c>
       <c r="R116" s="1">
-        <v>31106</v>
+        <v>31766</v>
       </c>
       <c r="S116" t="s">
-        <v>538</v>
+        <v>464</v>
       </c>
       <c r="T116" t="s">
         <v>27</v>
@@ -12934,10 +13036,10 @@
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="B117" t="s">
-        <v>540</v>
+        <v>466</v>
       </c>
       <c r="C117" t="s">
         <v>22</v>
@@ -12946,22 +13048,22 @@
         <v>23</v>
       </c>
       <c r="G117" s="1">
-        <v>46048</v>
+        <v>45902</v>
       </c>
       <c r="I117" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J117" t="s">
-        <v>541</v>
+        <v>33</v>
       </c>
       <c r="K117" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="L117">
-        <v>12182274808</v>
+        <v>12167306156</v>
       </c>
       <c r="M117">
-        <v>333370104</v>
+        <v>317358855</v>
       </c>
       <c r="N117" t="s">
         <v>27</v>
@@ -12970,16 +13072,16 @@
         <v>27</v>
       </c>
       <c r="P117" t="s">
-        <v>542</v>
+        <v>467</v>
       </c>
       <c r="Q117" t="s">
         <v>27</v>
       </c>
       <c r="R117" s="1">
-        <v>36422</v>
+        <v>34437</v>
       </c>
       <c r="S117" t="s">
-        <v>543</v>
+        <v>468</v>
       </c>
       <c r="T117" t="s">
         <v>27</v>
@@ -12987,10 +13089,10 @@
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>544</v>
+        <v>469</v>
       </c>
       <c r="B118" t="s">
-        <v>545</v>
+        <v>470</v>
       </c>
       <c r="C118" t="s">
         <v>22</v>
@@ -12999,22 +13101,22 @@
         <v>23</v>
       </c>
       <c r="G118" s="1">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="I118" t="s">
         <v>32</v>
       </c>
       <c r="J118" t="s">
-        <v>546</v>
+        <v>129</v>
       </c>
       <c r="K118" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="L118">
-        <v>12178450524</v>
+        <v>12182917078</v>
       </c>
       <c r="M118">
-        <v>329352768</v>
+        <v>335769594</v>
       </c>
       <c r="N118" t="s">
         <v>27</v>
@@ -13023,16 +13125,16 @@
         <v>27</v>
       </c>
       <c r="P118" t="s">
-        <v>547</v>
+        <v>471</v>
       </c>
       <c r="Q118" t="s">
         <v>27</v>
       </c>
       <c r="R118" s="1">
-        <v>29009</v>
+        <v>31756</v>
       </c>
       <c r="S118" t="s">
-        <v>548</v>
+        <v>472</v>
       </c>
       <c r="T118" t="s">
         <v>27</v>
@@ -13040,10 +13142,10 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>549</v>
+        <v>473</v>
       </c>
       <c r="B119" t="s">
-        <v>550</v>
+        <v>474</v>
       </c>
       <c r="C119" t="s">
         <v>22</v>
@@ -13052,22 +13154,22 @@
         <v>23</v>
       </c>
       <c r="G119" s="1">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="I119" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J119" t="s">
-        <v>551</v>
+        <v>33</v>
       </c>
       <c r="K119" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L119">
-        <v>12178179544</v>
+        <v>12175238375</v>
       </c>
       <c r="M119">
-        <v>328868760</v>
+        <v>325064172</v>
       </c>
       <c r="N119" t="s">
         <v>27</v>
@@ -13076,16 +13178,16 @@
         <v>27</v>
       </c>
       <c r="P119" t="s">
-        <v>552</v>
+        <v>475</v>
       </c>
       <c r="Q119" t="s">
         <v>27</v>
       </c>
       <c r="R119" s="1">
-        <v>29933</v>
+        <v>34435</v>
       </c>
       <c r="S119" t="s">
-        <v>553</v>
+        <v>476</v>
       </c>
       <c r="T119" t="s">
         <v>27</v>
@@ -13093,37 +13195,34 @@
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>554</v>
+        <v>477</v>
       </c>
       <c r="B120" t="s">
-        <v>555</v>
+        <v>478</v>
       </c>
       <c r="C120" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="D120" t="s">
         <v>23</v>
       </c>
-      <c r="E120">
-        <v>45870</v>
-      </c>
       <c r="G120" s="1">
-        <v>45873</v>
+        <v>46104</v>
       </c>
       <c r="I120" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J120" t="s">
-        <v>556</v>
+        <v>479</v>
       </c>
       <c r="K120" t="s">
-        <v>557</v>
+        <v>34</v>
       </c>
       <c r="L120">
-        <v>12176476097</v>
+        <v>12183153716</v>
       </c>
       <c r="M120">
-        <v>326513191</v>
+        <v>333148940</v>
       </c>
       <c r="N120" t="s">
         <v>27</v>
@@ -13132,16 +13231,16 @@
         <v>27</v>
       </c>
       <c r="P120" t="s">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="Q120" t="s">
         <v>27</v>
       </c>
       <c r="R120" s="1">
-        <v>36101</v>
+        <v>31149</v>
       </c>
       <c r="S120" t="s">
-        <v>559</v>
+        <v>481</v>
       </c>
       <c r="T120" t="s">
         <v>27</v>
@@ -13149,10 +13248,10 @@
     </row>
     <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>560</v>
+        <v>482</v>
       </c>
       <c r="B121" t="s">
-        <v>561</v>
+        <v>483</v>
       </c>
       <c r="C121" t="s">
         <v>22</v>
@@ -13161,22 +13260,22 @@
         <v>23</v>
       </c>
       <c r="G121" s="1">
-        <v>45873</v>
+        <v>45887</v>
       </c>
       <c r="I121" t="s">
         <v>32</v>
       </c>
       <c r="J121" t="s">
-        <v>169</v>
+        <v>484</v>
       </c>
       <c r="K121" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="L121">
-        <v>12178420892</v>
+        <v>12175808914</v>
       </c>
       <c r="M121">
-        <v>329332848</v>
+        <v>325618283</v>
       </c>
       <c r="N121" t="s">
         <v>27</v>
@@ -13185,16 +13284,16 @@
         <v>27</v>
       </c>
       <c r="P121" t="s">
-        <v>562</v>
+        <v>485</v>
       </c>
       <c r="Q121" t="s">
         <v>27</v>
       </c>
       <c r="R121" s="1">
-        <v>30664</v>
+        <v>31428</v>
       </c>
       <c r="S121" t="s">
-        <v>563</v>
+        <v>486</v>
       </c>
       <c r="T121" t="s">
         <v>27</v>
@@ -13202,34 +13301,34 @@
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>564</v>
+        <v>487</v>
       </c>
       <c r="B122" t="s">
-        <v>565</v>
+        <v>488</v>
       </c>
       <c r="C122" t="s">
         <v>22</v>
       </c>
       <c r="D122" t="s">
-        <v>566</v>
+        <v>23</v>
       </c>
       <c r="G122" s="1">
-        <v>46118</v>
+        <v>46028</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J122" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="K122" t="s">
         <v>47</v>
       </c>
       <c r="L122">
-        <v>12127227130</v>
+        <v>12177579535</v>
       </c>
       <c r="M122">
-        <v>315159731</v>
+        <v>327803886</v>
       </c>
       <c r="N122" t="s">
         <v>27</v>
@@ -13238,16 +13337,16 @@
         <v>27</v>
       </c>
       <c r="P122" t="s">
-        <v>567</v>
+        <v>489</v>
       </c>
       <c r="Q122" t="s">
         <v>27</v>
       </c>
       <c r="R122" s="1">
-        <v>31741</v>
+        <v>32239</v>
       </c>
       <c r="S122" t="s">
-        <v>568</v>
+        <v>490</v>
       </c>
       <c r="T122" t="s">
         <v>27</v>
@@ -13255,10 +13354,10 @@
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>569</v>
+        <v>491</v>
       </c>
       <c r="B123" t="s">
-        <v>570</v>
+        <v>492</v>
       </c>
       <c r="C123" t="s">
         <v>22</v>
@@ -13267,22 +13366,22 @@
         <v>23</v>
       </c>
       <c r="G123" s="1">
-        <v>45873</v>
+        <v>46066</v>
       </c>
       <c r="I123" t="s">
         <v>32</v>
       </c>
       <c r="J123" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="K123" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L123">
-        <v>12087500141</v>
+        <v>12178131437</v>
       </c>
       <c r="M123">
-        <v>307697410</v>
+        <v>328297852</v>
       </c>
       <c r="N123" t="s">
         <v>27</v>
@@ -13291,16 +13390,16 @@
         <v>27</v>
       </c>
       <c r="P123" t="s">
-        <v>571</v>
+        <v>493</v>
       </c>
       <c r="Q123" t="s">
         <v>27</v>
       </c>
       <c r="R123" s="1">
-        <v>32475</v>
+        <v>31004</v>
       </c>
       <c r="S123" t="s">
-        <v>572</v>
+        <v>494</v>
       </c>
       <c r="T123" t="s">
         <v>27</v>
@@ -13308,10 +13407,10 @@
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>573</v>
+        <v>495</v>
       </c>
       <c r="B124" t="s">
-        <v>574</v>
+        <v>496</v>
       </c>
       <c r="C124" t="s">
         <v>22</v>
@@ -13320,22 +13419,22 @@
         <v>23</v>
       </c>
       <c r="G124" s="1">
-        <v>45931</v>
+        <v>46055</v>
       </c>
       <c r="I124" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J124" t="s">
-        <v>255</v>
+        <v>109</v>
       </c>
       <c r="K124" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="L124">
-        <v>12171368537</v>
+        <v>12176382716</v>
       </c>
       <c r="M124">
-        <v>320614379</v>
+        <v>326243879</v>
       </c>
       <c r="N124" t="s">
         <v>27</v>
@@ -13344,16 +13443,16 @@
         <v>27</v>
       </c>
       <c r="P124" t="s">
-        <v>575</v>
+        <v>497</v>
       </c>
       <c r="Q124" t="s">
         <v>27</v>
       </c>
       <c r="R124" s="1">
-        <v>34397</v>
+        <v>30353</v>
       </c>
       <c r="S124" t="s">
-        <v>576</v>
+        <v>498</v>
       </c>
       <c r="T124" t="s">
         <v>27</v>
@@ -13361,10 +13460,10 @@
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>577</v>
+        <v>499</v>
       </c>
       <c r="B125" t="s">
-        <v>578</v>
+        <v>500</v>
       </c>
       <c r="C125" t="s">
         <v>22</v>
@@ -13373,17 +13472,23 @@
         <v>23</v>
       </c>
       <c r="G125" s="1">
-        <v>46055</v>
+        <v>45926</v>
       </c>
       <c r="I125" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J125" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="K125" t="s">
         <v>34</v>
       </c>
+      <c r="L125">
+        <v>12088460498</v>
+      </c>
+      <c r="M125">
+        <v>308483820</v>
+      </c>
       <c r="N125" t="s">
         <v>27</v>
       </c>
@@ -13391,16 +13496,16 @@
         <v>27</v>
       </c>
       <c r="P125" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="Q125" t="s">
         <v>27</v>
       </c>
       <c r="R125" s="1">
-        <v>33961</v>
+        <v>27288</v>
       </c>
       <c r="S125" t="s">
-        <v>27</v>
+        <v>502</v>
       </c>
       <c r="T125" t="s">
         <v>27</v>
@@ -13408,10 +13513,10 @@
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>580</v>
+        <v>503</v>
       </c>
       <c r="B126" t="s">
-        <v>581</v>
+        <v>504</v>
       </c>
       <c r="C126" t="s">
         <v>22</v>
@@ -13420,22 +13525,22 @@
         <v>23</v>
       </c>
       <c r="G126" s="1">
-        <v>45965</v>
+        <v>46055</v>
       </c>
       <c r="I126" t="s">
         <v>32</v>
       </c>
       <c r="J126" t="s">
-        <v>150</v>
+        <v>33</v>
       </c>
       <c r="K126" t="s">
         <v>47</v>
       </c>
       <c r="L126">
-        <v>12179353501</v>
+        <v>12176031515</v>
       </c>
       <c r="M126">
-        <v>330064070</v>
+        <v>325892270</v>
       </c>
       <c r="N126" t="s">
         <v>27</v>
@@ -13444,16 +13549,16 @@
         <v>27</v>
       </c>
       <c r="P126" t="s">
-        <v>582</v>
+        <v>505</v>
       </c>
       <c r="Q126" t="s">
         <v>27</v>
       </c>
       <c r="R126" s="1">
-        <v>28053</v>
+        <v>27347</v>
       </c>
       <c r="S126" t="s">
-        <v>583</v>
+        <v>506</v>
       </c>
       <c r="T126" t="s">
         <v>27</v>
@@ -13461,10 +13566,10 @@
     </row>
     <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>584</v>
+        <v>507</v>
       </c>
       <c r="B127" t="s">
-        <v>585</v>
+        <v>508</v>
       </c>
       <c r="C127" t="s">
         <v>22</v>
@@ -13473,22 +13578,22 @@
         <v>23</v>
       </c>
       <c r="G127" s="1">
-        <v>46041</v>
+        <v>46065</v>
       </c>
       <c r="I127" t="s">
         <v>32</v>
       </c>
       <c r="J127" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="K127" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="L127">
-        <v>12181505103</v>
+        <v>12178337176</v>
       </c>
       <c r="M127">
-        <v>333821025</v>
+        <v>329281011</v>
       </c>
       <c r="N127" t="s">
         <v>27</v>
@@ -13497,16 +13602,16 @@
         <v>27</v>
       </c>
       <c r="P127" t="s">
-        <v>586</v>
+        <v>509</v>
       </c>
       <c r="Q127" t="s">
         <v>27</v>
       </c>
       <c r="R127" s="1">
-        <v>30399</v>
+        <v>24624</v>
       </c>
       <c r="S127" t="s">
-        <v>587</v>
+        <v>510</v>
       </c>
       <c r="T127" t="s">
         <v>27</v>
@@ -13514,10 +13619,10 @@
     </row>
     <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>588</v>
+        <v>511</v>
       </c>
       <c r="B128" t="s">
-        <v>589</v>
+        <v>512</v>
       </c>
       <c r="C128" t="s">
         <v>22</v>
@@ -13526,22 +13631,22 @@
         <v>23</v>
       </c>
       <c r="G128" s="1">
-        <v>46056</v>
+        <v>45931</v>
       </c>
       <c r="I128" t="s">
         <v>24</v>
       </c>
       <c r="J128" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="K128" t="s">
-        <v>47</v>
+        <v>288</v>
       </c>
       <c r="L128">
-        <v>12175527772</v>
+        <v>12091179354</v>
       </c>
       <c r="M128">
-        <v>325363471</v>
+        <v>311567088</v>
       </c>
       <c r="N128" t="s">
         <v>27</v>
@@ -13550,16 +13655,16 @@
         <v>27</v>
       </c>
       <c r="P128" t="s">
-        <v>590</v>
+        <v>513</v>
       </c>
       <c r="Q128" t="s">
         <v>27</v>
       </c>
       <c r="R128" s="1">
-        <v>34722</v>
+        <v>28379</v>
       </c>
       <c r="S128" t="s">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="T128" t="s">
         <v>27</v>
@@ -13567,10 +13672,10 @@
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>592</v>
+        <v>515</v>
       </c>
       <c r="B129" t="s">
-        <v>593</v>
+        <v>516</v>
       </c>
       <c r="C129" t="s">
         <v>22</v>
@@ -13579,22 +13684,22 @@
         <v>23</v>
       </c>
       <c r="G129" s="1">
-        <v>46072</v>
+        <v>46055</v>
       </c>
       <c r="I129" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J129" t="s">
-        <v>374</v>
+        <v>109</v>
       </c>
       <c r="K129" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="L129">
-        <v>12178153784</v>
+        <v>12180291059</v>
       </c>
       <c r="M129">
-        <v>328328359</v>
+        <v>331124432</v>
       </c>
       <c r="N129" t="s">
         <v>27</v>
@@ -13603,16 +13708,16 @@
         <v>27</v>
       </c>
       <c r="P129" t="s">
-        <v>594</v>
+        <v>517</v>
       </c>
       <c r="Q129" t="s">
         <v>27</v>
       </c>
       <c r="R129" s="1">
-        <v>31486</v>
+        <v>27529</v>
       </c>
       <c r="S129" t="s">
-        <v>595</v>
+        <v>518</v>
       </c>
       <c r="T129" t="s">
         <v>27</v>
@@ -13620,10 +13725,10 @@
     </row>
     <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>596</v>
+        <v>519</v>
       </c>
       <c r="B130" t="s">
-        <v>597</v>
+        <v>520</v>
       </c>
       <c r="C130" t="s">
         <v>22</v>
@@ -13632,22 +13737,22 @@
         <v>23</v>
       </c>
       <c r="G130" s="1">
-        <v>46056</v>
+        <v>45939</v>
       </c>
       <c r="I130" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J130" t="s">
-        <v>216</v>
+        <v>46</v>
       </c>
       <c r="K130" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="L130">
-        <v>12179291855</v>
+        <v>12178130775</v>
       </c>
       <c r="M130">
-        <v>330740776</v>
+        <v>328405256</v>
       </c>
       <c r="N130" t="s">
         <v>27</v>
@@ -13656,16 +13761,16 @@
         <v>27</v>
       </c>
       <c r="P130" t="s">
-        <v>598</v>
+        <v>521</v>
       </c>
       <c r="Q130" t="s">
         <v>27</v>
       </c>
       <c r="R130" s="1">
-        <v>33289</v>
+        <v>29133</v>
       </c>
       <c r="S130" t="s">
-        <v>599</v>
+        <v>522</v>
       </c>
       <c r="T130" t="s">
         <v>27</v>
@@ -13673,10 +13778,10 @@
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>600</v>
+        <v>523</v>
       </c>
       <c r="B131" t="s">
-        <v>601</v>
+        <v>524</v>
       </c>
       <c r="C131" t="s">
         <v>22</v>
@@ -13685,22 +13790,22 @@
         <v>23</v>
       </c>
       <c r="G131" s="1">
-        <v>46114</v>
+        <v>45980</v>
       </c>
       <c r="I131" t="s">
         <v>32</v>
       </c>
       <c r="J131" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="K131" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L131">
-        <v>12182867634</v>
+        <v>12181939360</v>
       </c>
       <c r="M131">
-        <v>335536069</v>
+        <v>334654149</v>
       </c>
       <c r="N131" t="s">
         <v>27</v>
@@ -13709,16 +13814,16 @@
         <v>27</v>
       </c>
       <c r="P131" t="s">
-        <v>602</v>
+        <v>525</v>
       </c>
       <c r="Q131" t="s">
         <v>27</v>
       </c>
       <c r="R131" s="1">
-        <v>34924</v>
+        <v>28075</v>
       </c>
       <c r="S131" t="s">
-        <v>603</v>
+        <v>526</v>
       </c>
       <c r="T131" t="s">
         <v>27</v>
@@ -13726,10 +13831,10 @@
     </row>
     <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>604</v>
+        <v>527</v>
       </c>
       <c r="B132" t="s">
-        <v>605</v>
+        <v>528</v>
       </c>
       <c r="C132" t="s">
         <v>22</v>
@@ -13738,22 +13843,22 @@
         <v>23</v>
       </c>
       <c r="G132" s="1">
-        <v>46070</v>
+        <v>46065</v>
       </c>
       <c r="I132" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J132" t="s">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="K132" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L132">
-        <v>12174712759</v>
+        <v>12181910725</v>
       </c>
       <c r="M132">
-        <v>324465190</v>
+        <v>331773473</v>
       </c>
       <c r="N132" t="s">
         <v>27</v>
@@ -13762,16 +13867,16 @@
         <v>27</v>
       </c>
       <c r="P132" t="s">
-        <v>606</v>
+        <v>529</v>
       </c>
       <c r="Q132" t="s">
         <v>27</v>
       </c>
       <c r="R132" s="1">
-        <v>31488</v>
+        <v>28183</v>
       </c>
       <c r="S132" t="s">
-        <v>607</v>
+        <v>530</v>
       </c>
       <c r="T132" t="s">
         <v>27</v>
@@ -13779,10 +13884,10 @@
     </row>
     <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>608</v>
+        <v>531</v>
       </c>
       <c r="B133" t="s">
-        <v>609</v>
+        <v>532</v>
       </c>
       <c r="C133" t="s">
         <v>22</v>
@@ -13791,7 +13896,7 @@
         <v>23</v>
       </c>
       <c r="G133" s="1">
-        <v>45945</v>
+        <v>46055</v>
       </c>
       <c r="I133" t="s">
         <v>32</v>
@@ -13803,10 +13908,10 @@
         <v>34</v>
       </c>
       <c r="L133">
-        <v>12177901328</v>
+        <v>12174324251</v>
       </c>
       <c r="M133">
-        <v>328020192</v>
+        <v>324044895</v>
       </c>
       <c r="N133" t="s">
         <v>27</v>
@@ -13815,16 +13920,16 @@
         <v>27</v>
       </c>
       <c r="P133" t="s">
-        <v>610</v>
+        <v>533</v>
       </c>
       <c r="Q133" t="s">
         <v>27</v>
       </c>
       <c r="R133" s="1">
-        <v>33551</v>
+        <v>30735</v>
       </c>
       <c r="S133" t="s">
-        <v>611</v>
+        <v>534</v>
       </c>
       <c r="T133" t="s">
         <v>27</v>
@@ -13832,10 +13937,10 @@
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>612</v>
+        <v>535</v>
       </c>
       <c r="B134" t="s">
-        <v>613</v>
+        <v>536</v>
       </c>
       <c r="C134" t="s">
         <v>22</v>
@@ -13844,22 +13949,22 @@
         <v>23</v>
       </c>
       <c r="G134" s="1">
-        <v>45987</v>
+        <v>46072</v>
       </c>
       <c r="I134" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J134" t="s">
-        <v>614</v>
+        <v>40</v>
       </c>
       <c r="K134" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="L134">
-        <v>12179148092</v>
+        <v>12177618206</v>
       </c>
       <c r="M134">
-        <v>330151908</v>
+        <v>328046370</v>
       </c>
       <c r="N134" t="s">
         <v>27</v>
@@ -13868,16 +13973,16 @@
         <v>27</v>
       </c>
       <c r="P134" t="s">
-        <v>615</v>
+        <v>537</v>
       </c>
       <c r="Q134" t="s">
         <v>27</v>
       </c>
       <c r="R134" s="1">
-        <v>32233</v>
+        <v>31106</v>
       </c>
       <c r="S134" t="s">
-        <v>616</v>
+        <v>538</v>
       </c>
       <c r="T134" t="s">
         <v>27</v>
@@ -13885,10 +13990,10 @@
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>617</v>
+        <v>539</v>
       </c>
       <c r="B135" t="s">
-        <v>618</v>
+        <v>540</v>
       </c>
       <c r="C135" t="s">
         <v>22</v>
@@ -13897,22 +14002,22 @@
         <v>23</v>
       </c>
       <c r="G135" s="1">
-        <v>46072</v>
+        <v>46048</v>
       </c>
       <c r="I135" t="s">
         <v>24</v>
       </c>
       <c r="J135" t="s">
-        <v>135</v>
+        <v>541</v>
       </c>
       <c r="K135" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L135">
-        <v>12186649897</v>
+        <v>12182274808</v>
       </c>
       <c r="M135">
-        <v>326637869</v>
+        <v>333370104</v>
       </c>
       <c r="N135" t="s">
         <v>27</v>
@@ -13921,16 +14026,16 @@
         <v>27</v>
       </c>
       <c r="P135" t="s">
-        <v>619</v>
+        <v>542</v>
       </c>
       <c r="Q135" t="s">
         <v>27</v>
       </c>
       <c r="R135" s="1">
-        <v>30382</v>
+        <v>36422</v>
       </c>
       <c r="S135" t="s">
-        <v>620</v>
+        <v>543</v>
       </c>
       <c r="T135" t="s">
         <v>27</v>
@@ -13938,37 +14043,34 @@
     </row>
     <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>621</v>
+        <v>544</v>
       </c>
       <c r="B136" t="s">
-        <v>622</v>
+        <v>545</v>
       </c>
       <c r="C136" t="s">
-        <v>623</v>
+        <v>22</v>
       </c>
       <c r="D136" t="s">
-        <v>624</v>
-      </c>
-      <c r="F136">
-        <v>46119</v>
+        <v>23</v>
       </c>
       <c r="G136" s="1">
-        <v>45931</v>
+        <v>46049</v>
       </c>
       <c r="I136" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J136" t="s">
-        <v>255</v>
+        <v>546</v>
       </c>
       <c r="K136" t="s">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="L136">
-        <v>12176261986</v>
+        <v>12178450524</v>
       </c>
       <c r="M136">
-        <v>326176748</v>
+        <v>329352768</v>
       </c>
       <c r="N136" t="s">
         <v>27</v>
@@ -13977,16 +14079,16 @@
         <v>27</v>
       </c>
       <c r="P136" t="s">
-        <v>625</v>
+        <v>547</v>
       </c>
       <c r="Q136" t="s">
         <v>27</v>
       </c>
       <c r="R136" s="1">
-        <v>33112</v>
+        <v>29009</v>
       </c>
       <c r="S136" t="s">
-        <v>626</v>
+        <v>548</v>
       </c>
       <c r="T136" t="s">
         <v>27</v>
@@ -13994,40 +14096,34 @@
     </row>
     <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>627</v>
+        <v>549</v>
       </c>
       <c r="B137" t="s">
-        <v>628</v>
+        <v>550</v>
       </c>
       <c r="C137" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D137" t="s">
-        <v>630</v>
-      </c>
-      <c r="F137">
-        <v>46084</v>
+        <v>23</v>
       </c>
       <c r="G137" s="1">
-        <v>45931</v>
-      </c>
-      <c r="H137" s="1">
-        <v>46084</v>
+        <v>46056</v>
       </c>
       <c r="I137" t="s">
         <v>24</v>
       </c>
       <c r="J137" t="s">
-        <v>255</v>
+        <v>551</v>
       </c>
       <c r="K137" t="s">
         <v>47</v>
       </c>
       <c r="L137">
-        <v>12176457795</v>
+        <v>12178179544</v>
       </c>
       <c r="M137">
-        <v>326398414</v>
+        <v>328868760</v>
       </c>
       <c r="N137" t="s">
         <v>27</v>
@@ -14036,16 +14132,16 @@
         <v>27</v>
       </c>
       <c r="P137" t="s">
-        <v>631</v>
+        <v>552</v>
       </c>
       <c r="Q137" t="s">
         <v>27</v>
       </c>
       <c r="R137" s="1">
-        <v>31109</v>
+        <v>29933</v>
       </c>
       <c r="S137" t="s">
-        <v>632</v>
+        <v>553</v>
       </c>
       <c r="T137" t="s">
         <v>27</v>
@@ -14053,40 +14149,37 @@
     </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>633</v>
+        <v>554</v>
       </c>
       <c r="B138" t="s">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="C138" t="s">
-        <v>629</v>
+        <v>155</v>
       </c>
       <c r="D138" t="s">
-        <v>630</v>
-      </c>
-      <c r="F138">
-        <v>46087</v>
+        <v>23</v>
+      </c>
+      <c r="E138">
+        <v>45870</v>
       </c>
       <c r="G138" s="1">
-        <v>46076</v>
-      </c>
-      <c r="H138" s="1">
-        <v>46087</v>
+        <v>45873</v>
       </c>
       <c r="I138" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J138" t="s">
-        <v>135</v>
+        <v>556</v>
       </c>
       <c r="K138" t="s">
-        <v>47</v>
+        <v>557</v>
       </c>
       <c r="L138">
-        <v>12179964579</v>
+        <v>12176476097</v>
       </c>
       <c r="M138">
-        <v>331659352</v>
+        <v>326513191</v>
       </c>
       <c r="N138" t="s">
         <v>27</v>
@@ -14095,16 +14188,16 @@
         <v>27</v>
       </c>
       <c r="P138" t="s">
-        <v>635</v>
+        <v>558</v>
       </c>
       <c r="Q138" t="s">
         <v>27</v>
       </c>
       <c r="R138" s="1">
-        <v>30525</v>
+        <v>36101</v>
       </c>
       <c r="S138" t="s">
-        <v>636</v>
+        <v>559</v>
       </c>
       <c r="T138" t="s">
         <v>27</v>
@@ -14112,40 +14205,34 @@
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>637</v>
+        <v>560</v>
       </c>
       <c r="B139" t="s">
-        <v>638</v>
+        <v>561</v>
       </c>
       <c r="C139" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D139" t="s">
-        <v>630</v>
-      </c>
-      <c r="F139">
-        <v>46087</v>
+        <v>23</v>
       </c>
       <c r="G139" s="1">
-        <v>45931</v>
-      </c>
-      <c r="H139" s="1">
-        <v>46087</v>
+        <v>45873</v>
       </c>
       <c r="I139" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J139" t="s">
-        <v>255</v>
+        <v>169</v>
       </c>
       <c r="K139" t="s">
-        <v>337</v>
+        <v>47</v>
       </c>
       <c r="L139">
-        <v>12176565967</v>
+        <v>12178420892</v>
       </c>
       <c r="M139">
-        <v>326546413</v>
+        <v>329332848</v>
       </c>
       <c r="N139" t="s">
         <v>27</v>
@@ -14154,16 +14241,16 @@
         <v>27</v>
       </c>
       <c r="P139" t="s">
-        <v>639</v>
+        <v>562</v>
       </c>
       <c r="Q139" t="s">
         <v>27</v>
       </c>
       <c r="R139" s="1">
-        <v>29726</v>
+        <v>30664</v>
       </c>
       <c r="S139" t="s">
-        <v>640</v>
+        <v>563</v>
       </c>
       <c r="T139" t="s">
         <v>27</v>
@@ -14171,40 +14258,34 @@
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>641</v>
+        <v>564</v>
       </c>
       <c r="B140" t="s">
-        <v>642</v>
+        <v>565</v>
       </c>
       <c r="C140" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D140" t="s">
-        <v>630</v>
-      </c>
-      <c r="F140">
-        <v>46090</v>
+        <v>566</v>
       </c>
       <c r="G140" s="1">
-        <v>46055</v>
-      </c>
-      <c r="H140" s="1">
-        <v>46090</v>
+        <v>46118</v>
       </c>
       <c r="I140" t="s">
         <v>32</v>
       </c>
       <c r="J140" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="K140" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="L140">
-        <v>12182162759</v>
+        <v>12127227130</v>
       </c>
       <c r="M140">
-        <v>334874181</v>
+        <v>315159731</v>
       </c>
       <c r="N140" t="s">
         <v>27</v>
@@ -14213,16 +14294,16 @@
         <v>27</v>
       </c>
       <c r="P140" t="s">
-        <v>643</v>
+        <v>567</v>
       </c>
       <c r="Q140" t="s">
         <v>27</v>
       </c>
       <c r="R140" s="1">
-        <v>33972</v>
+        <v>31741</v>
       </c>
       <c r="S140" t="s">
-        <v>644</v>
+        <v>568</v>
       </c>
       <c r="T140" t="s">
         <v>27</v>
@@ -14230,40 +14311,34 @@
     </row>
     <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>645</v>
+        <v>569</v>
       </c>
       <c r="B141" t="s">
-        <v>646</v>
+        <v>570</v>
       </c>
       <c r="C141" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D141" t="s">
-        <v>630</v>
-      </c>
-      <c r="F141">
-        <v>46090</v>
+        <v>23</v>
       </c>
       <c r="G141" s="1">
-        <v>46055</v>
-      </c>
-      <c r="H141" s="1">
-        <v>46090</v>
+        <v>45873</v>
       </c>
       <c r="I141" t="s">
         <v>32</v>
       </c>
       <c r="J141" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="K141" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="L141">
-        <v>12182029339</v>
+        <v>12087500141</v>
       </c>
       <c r="M141">
-        <v>332535398</v>
+        <v>307697410</v>
       </c>
       <c r="N141" t="s">
         <v>27</v>
@@ -14272,16 +14347,16 @@
         <v>27</v>
       </c>
       <c r="P141" t="s">
-        <v>647</v>
+        <v>571</v>
       </c>
       <c r="Q141" t="s">
         <v>27</v>
       </c>
       <c r="R141" s="1">
-        <v>29437</v>
+        <v>32475</v>
       </c>
       <c r="S141" t="s">
-        <v>648</v>
+        <v>572</v>
       </c>
       <c r="T141" t="s">
         <v>27</v>
@@ -14289,25 +14364,19 @@
     </row>
     <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>649</v>
+        <v>573</v>
       </c>
       <c r="B142" t="s">
-        <v>650</v>
+        <v>574</v>
       </c>
       <c r="C142" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D142" t="s">
-        <v>630</v>
-      </c>
-      <c r="F142">
-        <v>46091</v>
+        <v>23</v>
       </c>
       <c r="G142" s="1">
-        <v>46030</v>
-      </c>
-      <c r="H142" s="1">
-        <v>46091</v>
+        <v>45931</v>
       </c>
       <c r="I142" t="s">
         <v>24</v>
@@ -14316,13 +14385,13 @@
         <v>255</v>
       </c>
       <c r="K142" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="L142">
-        <v>12177520975</v>
+        <v>12171368537</v>
       </c>
       <c r="M142">
-        <v>327472006</v>
+        <v>320614379</v>
       </c>
       <c r="N142" t="s">
         <v>27</v>
@@ -14331,16 +14400,16 @@
         <v>27</v>
       </c>
       <c r="P142" t="s">
-        <v>651</v>
+        <v>575</v>
       </c>
       <c r="Q142" t="s">
         <v>27</v>
       </c>
       <c r="R142" s="1">
-        <v>29451</v>
+        <v>34397</v>
       </c>
       <c r="S142" t="s">
-        <v>652</v>
+        <v>576</v>
       </c>
       <c r="T142" t="s">
         <v>27</v>
@@ -14348,40 +14417,28 @@
     </row>
     <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>653</v>
+        <v>577</v>
       </c>
       <c r="B143" t="s">
-        <v>654</v>
+        <v>578</v>
       </c>
       <c r="C143" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D143" t="s">
-        <v>630</v>
-      </c>
-      <c r="F143">
-        <v>46091</v>
+        <v>23</v>
       </c>
       <c r="G143" s="1">
-        <v>45931</v>
-      </c>
-      <c r="H143" s="1">
-        <v>46091</v>
+        <v>46055</v>
       </c>
       <c r="I143" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J143" t="s">
-        <v>255</v>
+        <v>33</v>
       </c>
       <c r="K143" t="s">
-        <v>53</v>
-      </c>
-      <c r="L143">
-        <v>12173757775</v>
-      </c>
-      <c r="M143">
-        <v>323169481</v>
+        <v>34</v>
       </c>
       <c r="N143" t="s">
         <v>27</v>
@@ -14390,16 +14447,16 @@
         <v>27</v>
       </c>
       <c r="P143" t="s">
-        <v>655</v>
+        <v>579</v>
       </c>
       <c r="Q143" t="s">
         <v>27</v>
       </c>
       <c r="R143" s="1">
-        <v>31807</v>
+        <v>33961</v>
       </c>
       <c r="S143" t="s">
-        <v>656</v>
+        <v>27</v>
       </c>
       <c r="T143" t="s">
         <v>27</v>
@@ -14407,40 +14464,34 @@
     </row>
     <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>657</v>
+        <v>580</v>
       </c>
       <c r="B144" t="s">
-        <v>658</v>
+        <v>581</v>
       </c>
       <c r="C144" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D144" t="s">
-        <v>630</v>
-      </c>
-      <c r="F144">
-        <v>46091</v>
+        <v>23</v>
       </c>
       <c r="G144" s="1">
-        <v>46076</v>
-      </c>
-      <c r="H144" s="1">
-        <v>46091</v>
+        <v>45965</v>
       </c>
       <c r="I144" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J144" t="s">
-        <v>659</v>
+        <v>150</v>
       </c>
       <c r="K144" t="s">
-        <v>660</v>
+        <v>47</v>
       </c>
       <c r="L144">
-        <v>12181820012</v>
+        <v>12179353501</v>
       </c>
       <c r="M144">
-        <v>33456465</v>
+        <v>330064070</v>
       </c>
       <c r="N144" t="s">
         <v>27</v>
@@ -14449,16 +14500,16 @@
         <v>27</v>
       </c>
       <c r="P144" t="s">
-        <v>661</v>
+        <v>582</v>
       </c>
       <c r="Q144" t="s">
         <v>27</v>
       </c>
       <c r="R144" s="1">
-        <v>27200</v>
+        <v>28053</v>
       </c>
       <c r="S144" t="s">
-        <v>662</v>
+        <v>583</v>
       </c>
       <c r="T144" t="s">
         <v>27</v>
@@ -14466,40 +14517,34 @@
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>663</v>
+        <v>584</v>
       </c>
       <c r="B145" t="s">
-        <v>664</v>
+        <v>585</v>
       </c>
       <c r="C145" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D145" t="s">
-        <v>630</v>
-      </c>
-      <c r="F145">
-        <v>46092</v>
+        <v>23</v>
       </c>
       <c r="G145" s="1">
-        <v>46035</v>
-      </c>
-      <c r="H145" s="1">
-        <v>46092</v>
+        <v>46041</v>
       </c>
       <c r="I145" t="s">
         <v>32</v>
       </c>
       <c r="J145" t="s">
-        <v>282</v>
+        <v>129</v>
       </c>
       <c r="K145" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="L145">
-        <v>12179725003</v>
+        <v>12181505103</v>
       </c>
       <c r="M145">
-        <v>331296845</v>
+        <v>333821025</v>
       </c>
       <c r="N145" t="s">
         <v>27</v>
@@ -14508,16 +14553,16 @@
         <v>27</v>
       </c>
       <c r="P145" t="s">
-        <v>665</v>
+        <v>586</v>
       </c>
       <c r="Q145" t="s">
         <v>27</v>
       </c>
       <c r="R145" s="1">
-        <v>27282</v>
+        <v>30399</v>
       </c>
       <c r="S145" t="s">
-        <v>666</v>
+        <v>587</v>
       </c>
       <c r="T145" t="s">
         <v>27</v>
@@ -14525,10 +14570,10 @@
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>667</v>
+        <v>588</v>
       </c>
       <c r="B146" t="s">
-        <v>668</v>
+        <v>589</v>
       </c>
       <c r="C146" t="s">
         <v>22</v>
@@ -14537,25 +14582,22 @@
         <v>23</v>
       </c>
       <c r="G146" s="1">
-        <v>46077</v>
-      </c>
-      <c r="H146" s="1">
-        <v>46094</v>
+        <v>46056</v>
       </c>
       <c r="I146" t="s">
-        <v>669</v>
+        <v>24</v>
       </c>
       <c r="J146" t="s">
-        <v>670</v>
+        <v>268</v>
       </c>
       <c r="K146" t="s">
         <v>47</v>
       </c>
       <c r="L146">
-        <v>12175735121</v>
+        <v>12175527772</v>
       </c>
       <c r="M146">
-        <v>325474346</v>
+        <v>325363471</v>
       </c>
       <c r="N146" t="s">
         <v>27</v>
@@ -14564,16 +14606,16 @@
         <v>27</v>
       </c>
       <c r="P146" t="s">
-        <v>671</v>
+        <v>590</v>
       </c>
       <c r="Q146" t="s">
         <v>27</v>
       </c>
       <c r="R146" s="1">
-        <v>31397</v>
+        <v>34722</v>
       </c>
       <c r="S146" t="s">
-        <v>672</v>
+        <v>591</v>
       </c>
       <c r="T146" t="s">
         <v>27</v>
@@ -14581,34 +14623,34 @@
     </row>
     <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>673</v>
+        <v>592</v>
       </c>
       <c r="B147" t="s">
-        <v>674</v>
+        <v>593</v>
       </c>
       <c r="C147" t="s">
         <v>22</v>
       </c>
       <c r="D147" t="s">
-        <v>675</v>
+        <v>23</v>
       </c>
       <c r="G147" s="1">
-        <v>46077</v>
-      </c>
-      <c r="H147" s="1">
-        <v>46094</v>
+        <v>46072</v>
       </c>
       <c r="I147" t="s">
-        <v>669</v>
+        <v>24</v>
       </c>
       <c r="J147" t="s">
-        <v>670</v>
+        <v>374</v>
       </c>
       <c r="K147" t="s">
-        <v>47</v>
+        <v>120</v>
+      </c>
+      <c r="L147">
+        <v>12178153784</v>
       </c>
       <c r="M147">
-        <v>332509311</v>
+        <v>328328359</v>
       </c>
       <c r="N147" t="s">
         <v>27</v>
@@ -14617,16 +14659,16 @@
         <v>27</v>
       </c>
       <c r="P147" t="s">
-        <v>676</v>
+        <v>594</v>
       </c>
       <c r="Q147" t="s">
         <v>27</v>
       </c>
       <c r="R147" s="1">
-        <v>34195</v>
+        <v>31486</v>
       </c>
       <c r="S147" t="s">
-        <v>677</v>
+        <v>595</v>
       </c>
       <c r="T147" t="s">
         <v>27</v>
@@ -14634,40 +14676,34 @@
     </row>
     <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>678</v>
+        <v>596</v>
       </c>
       <c r="B148" t="s">
-        <v>679</v>
+        <v>597</v>
       </c>
       <c r="C148" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D148" t="s">
-        <v>630</v>
-      </c>
-      <c r="F148">
-        <v>46095</v>
+        <v>23</v>
       </c>
       <c r="G148" s="1">
-        <v>46041</v>
-      </c>
-      <c r="H148" s="1">
-        <v>46095</v>
+        <v>46056</v>
       </c>
       <c r="I148" t="s">
         <v>24</v>
       </c>
       <c r="J148" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="K148" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L148">
-        <v>12176904334</v>
+        <v>12179291855</v>
       </c>
       <c r="M148">
-        <v>326894195</v>
+        <v>330740776</v>
       </c>
       <c r="N148" t="s">
         <v>27</v>
@@ -14676,16 +14712,16 @@
         <v>27</v>
       </c>
       <c r="P148" t="s">
-        <v>680</v>
+        <v>598</v>
       </c>
       <c r="Q148" t="s">
         <v>27</v>
       </c>
       <c r="R148" s="1">
-        <v>27164</v>
+        <v>33289</v>
       </c>
       <c r="S148" t="s">
-        <v>681</v>
+        <v>599</v>
       </c>
       <c r="T148" t="s">
         <v>27</v>
@@ -14693,40 +14729,34 @@
     </row>
     <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>682</v>
+        <v>600</v>
       </c>
       <c r="B149" t="s">
-        <v>683</v>
+        <v>601</v>
       </c>
       <c r="C149" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D149" t="s">
-        <v>630</v>
-      </c>
-      <c r="F149">
-        <v>46096</v>
+        <v>23</v>
       </c>
       <c r="G149" s="1">
-        <v>46028</v>
-      </c>
-      <c r="H149" s="1">
-        <v>46096</v>
+        <v>46114</v>
       </c>
       <c r="I149" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J149" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="K149" t="s">
         <v>41</v>
       </c>
       <c r="L149">
-        <v>12180291009</v>
+        <v>12182867634</v>
       </c>
       <c r="M149">
-        <v>331104202</v>
+        <v>335536069</v>
       </c>
       <c r="N149" t="s">
         <v>27</v>
@@ -14735,16 +14765,16 @@
         <v>27</v>
       </c>
       <c r="P149" t="s">
-        <v>684</v>
+        <v>602</v>
       </c>
       <c r="Q149" t="s">
         <v>27</v>
       </c>
       <c r="R149" s="1">
-        <v>27305</v>
+        <v>34924</v>
       </c>
       <c r="S149" t="s">
-        <v>685</v>
+        <v>603</v>
       </c>
       <c r="T149" t="s">
         <v>27</v>
@@ -14752,40 +14782,34 @@
     </row>
     <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>686</v>
+        <v>604</v>
       </c>
       <c r="B150" t="s">
-        <v>687</v>
+        <v>605</v>
       </c>
       <c r="C150" t="s">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="D150" t="s">
-        <v>630</v>
-      </c>
-      <c r="F150">
-        <v>46098</v>
+        <v>23</v>
       </c>
       <c r="G150" s="1">
-        <v>46055</v>
-      </c>
-      <c r="H150" s="1">
-        <v>46098</v>
+        <v>46070</v>
       </c>
       <c r="I150" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J150" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K150" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="L150">
-        <v>12178154462</v>
+        <v>12174712759</v>
       </c>
       <c r="M150">
-        <v>328809365</v>
+        <v>324465190</v>
       </c>
       <c r="N150" t="s">
         <v>27</v>
@@ -14794,16 +14818,16 @@
         <v>27</v>
       </c>
       <c r="P150" t="s">
-        <v>688</v>
+        <v>606</v>
       </c>
       <c r="Q150" t="s">
         <v>27</v>
       </c>
       <c r="R150" s="1">
-        <v>30597</v>
+        <v>31488</v>
       </c>
       <c r="S150" t="s">
-        <v>689</v>
+        <v>607</v>
       </c>
       <c r="T150" t="s">
         <v>27</v>
@@ -14811,40 +14835,34 @@
     </row>
     <row r="151" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>690</v>
+        <v>608</v>
       </c>
       <c r="B151" t="s">
-        <v>691</v>
+        <v>609</v>
       </c>
       <c r="C151" t="s">
-        <v>623</v>
+        <v>22</v>
       </c>
       <c r="D151" t="s">
-        <v>624</v>
-      </c>
-      <c r="F151">
-        <v>46104</v>
+        <v>23</v>
       </c>
       <c r="G151" s="1">
-        <v>46070</v>
-      </c>
-      <c r="H151" s="1">
-        <v>46104</v>
+        <v>45945</v>
       </c>
       <c r="I151" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J151" t="s">
-        <v>418</v>
+        <v>33</v>
       </c>
       <c r="K151" t="s">
-        <v>283</v>
+        <v>34</v>
       </c>
       <c r="L151">
-        <v>12182473225</v>
+        <v>12177901328</v>
       </c>
       <c r="M151">
-        <v>334932939</v>
+        <v>328020192</v>
       </c>
       <c r="N151" t="s">
         <v>27</v>
@@ -14853,16 +14871,16 @@
         <v>27</v>
       </c>
       <c r="P151" t="s">
-        <v>692</v>
+        <v>610</v>
       </c>
       <c r="Q151" t="s">
         <v>27</v>
       </c>
       <c r="R151" s="1">
-        <v>31246</v>
+        <v>33551</v>
       </c>
       <c r="S151" t="s">
-        <v>693</v>
+        <v>611</v>
       </c>
       <c r="T151" t="s">
         <v>27</v>
@@ -14870,40 +14888,34 @@
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>694</v>
+        <v>612</v>
       </c>
       <c r="B152" t="s">
-        <v>695</v>
+        <v>613</v>
       </c>
       <c r="C152" t="s">
-        <v>623</v>
+        <v>22</v>
       </c>
       <c r="D152" t="s">
-        <v>624</v>
-      </c>
-      <c r="F152">
-        <v>46106</v>
+        <v>23</v>
       </c>
       <c r="G152" s="1">
-        <v>46055</v>
-      </c>
-      <c r="H152" s="1">
-        <v>46106</v>
+        <v>45987</v>
       </c>
       <c r="I152" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J152" t="s">
-        <v>696</v>
+        <v>614</v>
       </c>
       <c r="K152" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L152">
-        <v>12179713068</v>
+        <v>12179148092</v>
       </c>
       <c r="M152">
-        <v>331127750</v>
+        <v>330151908</v>
       </c>
       <c r="N152" t="s">
         <v>27</v>
@@ -14912,16 +14924,16 @@
         <v>27</v>
       </c>
       <c r="P152" t="s">
-        <v>697</v>
+        <v>615</v>
       </c>
       <c r="Q152" t="s">
         <v>27</v>
       </c>
       <c r="R152" s="1">
-        <v>32407</v>
+        <v>32233</v>
       </c>
       <c r="S152" t="s">
-        <v>698</v>
+        <v>616</v>
       </c>
       <c r="T152" t="s">
         <v>27</v>
@@ -14929,40 +14941,34 @@
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>699</v>
+        <v>617</v>
       </c>
       <c r="B153" t="s">
-        <v>700</v>
+        <v>618</v>
       </c>
       <c r="C153" t="s">
-        <v>623</v>
+        <v>22</v>
       </c>
       <c r="D153" t="s">
-        <v>624</v>
-      </c>
-      <c r="F153">
-        <v>46111</v>
+        <v>23</v>
       </c>
       <c r="G153" s="1">
-        <v>45931</v>
-      </c>
-      <c r="H153" s="1">
-        <v>46111</v>
+        <v>46072</v>
       </c>
       <c r="I153" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J153" t="s">
-        <v>701</v>
+        <v>135</v>
       </c>
       <c r="K153" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="L153">
-        <v>12178058358</v>
+        <v>12186649897</v>
       </c>
       <c r="M153">
-        <v>328805408</v>
+        <v>326637869</v>
       </c>
       <c r="N153" t="s">
         <v>27</v>
@@ -14971,16 +14977,16 @@
         <v>27</v>
       </c>
       <c r="P153" t="s">
-        <v>702</v>
+        <v>619</v>
       </c>
       <c r="Q153" t="s">
         <v>27</v>
       </c>
       <c r="R153" s="1">
-        <v>33345</v>
+        <v>30382</v>
       </c>
       <c r="S153" t="s">
-        <v>703</v>
+        <v>620</v>
       </c>
       <c r="T153" t="s">
         <v>27</v>
@@ -14988,10 +14994,10 @@
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>704</v>
+        <v>621</v>
       </c>
       <c r="B154" t="s">
-        <v>705</v>
+        <v>622</v>
       </c>
       <c r="C154" t="s">
         <v>623</v>
@@ -15000,28 +15006,25 @@
         <v>624</v>
       </c>
       <c r="F154">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="G154" s="1">
-        <v>46063</v>
-      </c>
-      <c r="H154" s="1">
-        <v>46113</v>
+        <v>45931</v>
       </c>
       <c r="I154" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J154" t="s">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="K154" t="s">
-        <v>130</v>
+        <v>337</v>
       </c>
       <c r="L154">
-        <v>12182388541</v>
+        <v>12176261986</v>
       </c>
       <c r="M154">
-        <v>335276407</v>
+        <v>326176748</v>
       </c>
       <c r="N154" t="s">
         <v>27</v>
@@ -15030,16 +15033,16 @@
         <v>27</v>
       </c>
       <c r="P154" t="s">
-        <v>706</v>
+        <v>625</v>
       </c>
       <c r="Q154" t="s">
         <v>27</v>
       </c>
       <c r="R154" s="1">
-        <v>33559</v>
+        <v>33112</v>
       </c>
       <c r="S154" t="s">
-        <v>707</v>
+        <v>626</v>
       </c>
       <c r="T154" t="s">
         <v>27</v>
